--- a/research/traditional_assets/database/data/spain/spain_beverage_alcoholic.xlsx
+++ b/research/traditional_assets/database/data/spain/spain_beverage_alcoholic.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09047399430661505</v>
+        <v>0.09028155932084851</v>
       </c>
       <c r="C2">
-        <v>37.07499190925823</v>
+        <v>36.83054118825129</v>
       </c>
       <c r="D2">
-        <v>36.87999190925823</v>
+        <v>37.03954118825129</v>
       </c>
       <c r="E2">
-        <v>-23.9</v>
+        <v>-23.496</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.404</v>
       </c>
       <c r="G2">
         <v>0.195</v>
@@ -1445,28 +1445,28 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.0203212</v>
       </c>
       <c r="N2">
-        <v>0.9866666666666668</v>
+        <v>0.9663454666666668</v>
       </c>
       <c r="O2">
-        <v>0.2466666666666667</v>
+        <v>0.2415863666666667</v>
       </c>
       <c r="P2">
-        <v>0.7400000000000001</v>
+        <v>0.7247591000000001</v>
       </c>
       <c r="Q2">
-        <v>2.72</v>
+        <v>2.7047591</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09047399430661505</v>
+        <v>0.09081243365742274</v>
       </c>
       <c r="T2">
-        <v>0.6910924838905986</v>
+        <v>0.6963280330109819</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>48.55356310979011</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09028155932084851</v>
+        <v>0.09008912433508198</v>
       </c>
       <c r="C3">
-        <v>36.83054118825129</v>
+        <v>36.58747694140444</v>
       </c>
       <c r="D3">
-        <v>37.03954118825129</v>
+        <v>37.20047694140444</v>
       </c>
       <c r="E3">
-        <v>-23.496</v>
+        <v>-23.092</v>
       </c>
       <c r="F3">
-        <v>0.404</v>
+        <v>0.8079999999999999</v>
       </c>
       <c r="G3">
         <v>0.195</v>
@@ -1527,28 +1527,28 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M3">
-        <v>0.0203212</v>
+        <v>0.0406424</v>
       </c>
       <c r="N3">
-        <v>0.9663454666666668</v>
+        <v>0.9460242666666668</v>
       </c>
       <c r="O3">
-        <v>0.2415863666666667</v>
+        <v>0.2365060666666667</v>
       </c>
       <c r="P3">
-        <v>0.7247591000000001</v>
+        <v>0.7095182000000001</v>
       </c>
       <c r="Q3">
-        <v>2.7047591</v>
+        <v>2.6895182</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09081243365742274</v>
+        <v>0.09115777993375712</v>
       </c>
       <c r="T3">
-        <v>0.6963280330109819</v>
+        <v>0.7016704300725977</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>48.55356310979011</v>
+        <v>24.27678155489506</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09008912433508198</v>
+        <v>0.08989668934931544</v>
       </c>
       <c r="C4">
-        <v>36.58747694140444</v>
+        <v>36.34581732015759</v>
       </c>
       <c r="D4">
-        <v>37.20047694140444</v>
+        <v>37.36281732015759</v>
       </c>
       <c r="E4">
-        <v>-23.092</v>
+        <v>-22.688</v>
       </c>
       <c r="F4">
-        <v>0.8079999999999999</v>
+        <v>1.212</v>
       </c>
       <c r="G4">
         <v>0.195</v>
@@ -1609,28 +1609,28 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M4">
-        <v>0.0406424</v>
+        <v>0.06096359999999999</v>
       </c>
       <c r="N4">
-        <v>0.9460242666666668</v>
+        <v>0.9257030666666668</v>
       </c>
       <c r="O4">
-        <v>0.2365060666666667</v>
+        <v>0.2314257666666667</v>
       </c>
       <c r="P4">
-        <v>0.7095182000000001</v>
+        <v>0.6942773000000001</v>
       </c>
       <c r="Q4">
-        <v>2.6895182</v>
+        <v>2.6742773</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09115777993375712</v>
+        <v>0.09151024675187158</v>
       </c>
       <c r="T4">
-        <v>0.7016704300725977</v>
+        <v>0.7071229796509475</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>24.27678155489506</v>
+        <v>16.18452103659671</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.08989668934931544</v>
+        <v>0.0897492543635489</v>
       </c>
       <c r="C5">
-        <v>36.34581732015759</v>
+        <v>36.06715702203804</v>
       </c>
       <c r="D5">
-        <v>37.36281732015759</v>
+        <v>37.48815702203804</v>
       </c>
       <c r="E5">
-        <v>-22.688</v>
+        <v>-22.284</v>
       </c>
       <c r="F5">
-        <v>1.212</v>
+        <v>1.616</v>
       </c>
       <c r="G5">
         <v>0.195</v>
@@ -1691,45 +1691,45 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M5">
-        <v>0.06096359999999999</v>
+        <v>0.08370879999999999</v>
       </c>
       <c r="N5">
-        <v>0.9257030666666668</v>
+        <v>0.9029578666666668</v>
       </c>
       <c r="O5">
-        <v>0.2314257666666667</v>
+        <v>0.2257394666666667</v>
       </c>
       <c r="P5">
-        <v>0.6942773000000001</v>
+        <v>0.6772184000000001</v>
       </c>
       <c r="Q5">
-        <v>2.6742773</v>
+        <v>2.6572184</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09151024675187158</v>
+        <v>0.09187005662869678</v>
       </c>
       <c r="T5">
-        <v>0.7071229796509475</v>
+        <v>0.7126891240121799</v>
       </c>
       <c r="U5">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V5">
         <v>0.25</v>
       </c>
       <c r="W5">
-        <v>0.03772499999999999</v>
+        <v>0.03885</v>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y5">
-        <v>16.18452103659671</v>
+        <v>11.78689297501179</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.0897492543635489</v>
+        <v>0.08963181937778236</v>
       </c>
       <c r="C6">
-        <v>36.06715702203804</v>
+        <v>35.76359595541547</v>
       </c>
       <c r="D6">
-        <v>37.48815702203804</v>
+        <v>37.58859595541547</v>
       </c>
       <c r="E6">
-        <v>-22.284</v>
+        <v>-21.88</v>
       </c>
       <c r="F6">
-        <v>1.616</v>
+        <v>2.02</v>
       </c>
       <c r="G6">
         <v>0.195</v>
@@ -1773,45 +1773,45 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M6">
-        <v>0.08370879999999999</v>
+        <v>0.10807</v>
       </c>
       <c r="N6">
-        <v>0.9029578666666668</v>
+        <v>0.8785966666666668</v>
       </c>
       <c r="O6">
-        <v>0.2257394666666667</v>
+        <v>0.2196491666666667</v>
       </c>
       <c r="P6">
-        <v>0.6772184000000001</v>
+        <v>0.6589475000000001</v>
       </c>
       <c r="Q6">
-        <v>2.6572184</v>
+        <v>2.6389475</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09187005662869678</v>
+        <v>0.09223744145029722</v>
       </c>
       <c r="T6">
-        <v>0.7126891240121799</v>
+        <v>0.7183724503599643</v>
       </c>
       <c r="U6">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V6">
         <v>0.25</v>
       </c>
       <c r="W6">
-        <v>0.03885</v>
+        <v>0.040125</v>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y6">
-        <v>11.78689297501179</v>
+        <v>9.129884951111935</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.08963181937778236</v>
+        <v>0.08949938439201584</v>
       </c>
       <c r="C7">
-        <v>35.76359595541547</v>
+        <v>35.47351163728601</v>
       </c>
       <c r="D7">
-        <v>37.58859595541547</v>
+        <v>37.70251163728601</v>
       </c>
       <c r="E7">
-        <v>-21.88</v>
+        <v>-21.476</v>
       </c>
       <c r="F7">
-        <v>2.02</v>
+        <v>2.424</v>
       </c>
       <c r="G7">
         <v>0.195</v>
@@ -1855,45 +1855,45 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M7">
-        <v>0.10807</v>
+        <v>0.1316232</v>
       </c>
       <c r="N7">
-        <v>0.8785966666666668</v>
+        <v>0.8550434666666669</v>
       </c>
       <c r="O7">
-        <v>0.2196491666666667</v>
+        <v>0.2137608666666667</v>
       </c>
       <c r="P7">
-        <v>0.6589475000000001</v>
+        <v>0.6412826000000001</v>
       </c>
       <c r="Q7">
-        <v>2.6389475</v>
+        <v>2.6212826</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09223744145029722</v>
+        <v>0.09261264297022961</v>
       </c>
       <c r="T7">
-        <v>0.7183724503599643</v>
+        <v>0.7241766985449358</v>
       </c>
       <c r="U7">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V7">
         <v>0.25</v>
       </c>
       <c r="W7">
-        <v>0.040125</v>
+        <v>0.040725</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y7">
-        <v>9.129884951111935</v>
+        <v>7.496145562990923</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.08949938439201584</v>
+        <v>0.0893369494062493</v>
       </c>
       <c r="C8">
-        <v>35.47351163728601</v>
+        <v>35.21017851966262</v>
       </c>
       <c r="D8">
-        <v>37.70251163728601</v>
+        <v>37.84317851966262</v>
       </c>
       <c r="E8">
-        <v>-21.476</v>
+        <v>-21.072</v>
       </c>
       <c r="F8">
-        <v>2.424</v>
+        <v>2.827999999999999</v>
       </c>
       <c r="G8">
         <v>0.195</v>
@@ -1937,28 +1937,28 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M8">
-        <v>0.1316232</v>
+        <v>0.1535604</v>
       </c>
       <c r="N8">
-        <v>0.8550434666666669</v>
+        <v>0.8331062666666669</v>
       </c>
       <c r="O8">
-        <v>0.2137608666666667</v>
+        <v>0.2082765666666667</v>
       </c>
       <c r="P8">
-        <v>0.6412826000000001</v>
+        <v>0.6248297000000002</v>
       </c>
       <c r="Q8">
-        <v>2.6212826</v>
+        <v>2.6048297</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09261264297022961</v>
+        <v>0.092995913340053</v>
       </c>
       <c r="T8">
-        <v>0.7241766985449358</v>
+        <v>0.7301057692715195</v>
       </c>
       <c r="U8">
         <v>0.0543</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>7.496145562990923</v>
+        <v>6.425267625420792</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.08933694940624928</v>
+        <v>0.08923451442048277</v>
       </c>
       <c r="C9">
-        <v>35.21017851966263</v>
+        <v>34.89542702410068</v>
       </c>
       <c r="D9">
-        <v>37.84317851966263</v>
+        <v>37.93242702410068</v>
       </c>
       <c r="E9">
-        <v>-21.072</v>
+        <v>-20.668</v>
       </c>
       <c r="F9">
-        <v>2.828</v>
+        <v>3.232</v>
       </c>
       <c r="G9">
         <v>0.195</v>
@@ -2019,45 +2019,45 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M9">
-        <v>0.1535604</v>
+        <v>0.1787296</v>
       </c>
       <c r="N9">
-        <v>0.8331062666666668</v>
+        <v>0.8079370666666668</v>
       </c>
       <c r="O9">
-        <v>0.2082765666666667</v>
+        <v>0.2019842666666667</v>
       </c>
       <c r="P9">
-        <v>0.6248297</v>
+        <v>0.6059528000000001</v>
       </c>
       <c r="Q9">
-        <v>2.6048297</v>
+        <v>2.5859528</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.092995913340053</v>
+        <v>0.09338751567443779</v>
       </c>
       <c r="T9">
-        <v>0.7301057692715195</v>
+        <v>0.7361637328399856</v>
       </c>
       <c r="U9">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V9">
         <v>0.25</v>
       </c>
       <c r="W9">
-        <v>0.040725</v>
+        <v>0.041475</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y9">
-        <v>6.42526762542079</v>
+        <v>5.520443545258686</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.08923451442048277</v>
+        <v>0.08907957943471621</v>
       </c>
       <c r="C10">
-        <v>34.89542702410068</v>
+        <v>34.62721993424056</v>
       </c>
       <c r="D10">
-        <v>37.93242702410068</v>
+        <v>38.06821993424056</v>
       </c>
       <c r="E10">
-        <v>-20.668</v>
+        <v>-20.264</v>
       </c>
       <c r="F10">
-        <v>3.232</v>
+        <v>3.636</v>
       </c>
       <c r="G10">
         <v>0.195</v>
@@ -2101,28 +2101,28 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M10">
-        <v>0.1787296</v>
+        <v>0.2010708</v>
       </c>
       <c r="N10">
-        <v>0.8079370666666668</v>
+        <v>0.7855958666666668</v>
       </c>
       <c r="O10">
-        <v>0.2019842666666667</v>
+        <v>0.1963989666666667</v>
       </c>
       <c r="P10">
-        <v>0.6059528000000001</v>
+        <v>0.5891969000000001</v>
       </c>
       <c r="Q10">
-        <v>2.5859528</v>
+        <v>2.5691969</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09338751567443779</v>
+        <v>0.0937877246535343</v>
       </c>
       <c r="T10">
-        <v>0.7361637328399856</v>
+        <v>0.7423548384649012</v>
       </c>
       <c r="U10">
         <v>0.0553</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>5.520443545258686</v>
+        <v>4.907060929118832</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.08907957943471621</v>
+        <v>0.08911214444894969</v>
       </c>
       <c r="C11">
-        <v>34.62721993424056</v>
+        <v>34.19459765890015</v>
       </c>
       <c r="D11">
-        <v>38.06821993424056</v>
+        <v>38.03959765890015</v>
       </c>
       <c r="E11">
-        <v>-20.264</v>
+        <v>-19.86</v>
       </c>
       <c r="F11">
-        <v>3.636</v>
+        <v>4.039999999999999</v>
       </c>
       <c r="G11">
         <v>0.195</v>
@@ -2183,45 +2183,45 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M11">
-        <v>0.2010708</v>
+        <v>0.233512</v>
       </c>
       <c r="N11">
-        <v>0.7855958666666668</v>
+        <v>0.7531546666666669</v>
       </c>
       <c r="O11">
-        <v>0.1963989666666667</v>
+        <v>0.1882886666666667</v>
       </c>
       <c r="P11">
-        <v>0.5891969000000001</v>
+        <v>0.5648660000000001</v>
       </c>
       <c r="Q11">
-        <v>2.5691969</v>
+        <v>2.544866</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.0937877246535343</v>
+        <v>0.09419682716549964</v>
       </c>
       <c r="T11">
-        <v>0.7423548384649012</v>
+        <v>0.7486835242148151</v>
       </c>
       <c r="U11">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V11">
         <v>0.25</v>
       </c>
       <c r="W11">
-        <v>0.041475</v>
+        <v>0.04335</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y11">
-        <v>4.907060929118832</v>
+        <v>4.225336028412531</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.08911214444894969</v>
+        <v>0.08926470946318314</v>
       </c>
       <c r="C12">
-        <v>34.19459765890015</v>
+        <v>33.65707527188912</v>
       </c>
       <c r="D12">
-        <v>38.03959765890015</v>
+        <v>37.90607527188912</v>
       </c>
       <c r="E12">
-        <v>-19.86</v>
+        <v>-19.456</v>
       </c>
       <c r="F12">
-        <v>4.04</v>
+        <v>4.444</v>
       </c>
       <c r="G12">
         <v>0.195</v>
@@ -2265,45 +2265,45 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M12">
-        <v>0.233512</v>
+        <v>0.2724172</v>
       </c>
       <c r="N12">
-        <v>0.7531546666666667</v>
+        <v>0.7142494666666668</v>
       </c>
       <c r="O12">
-        <v>0.1882886666666667</v>
+        <v>0.1785623666666667</v>
       </c>
       <c r="P12">
-        <v>0.5648660000000001</v>
+        <v>0.5356871000000001</v>
       </c>
       <c r="Q12">
-        <v>2.544866</v>
+        <v>2.5156871</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09419682716549964</v>
+        <v>0.09461512299234061</v>
       </c>
       <c r="T12">
-        <v>0.7486835242148151</v>
+        <v>0.7551544276220306</v>
       </c>
       <c r="U12">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V12">
         <v>0.25</v>
       </c>
       <c r="W12">
-        <v>0.04335</v>
+        <v>0.045975</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y12">
-        <v>4.22533602841253</v>
+        <v>3.621895631651256</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.08926470946318314</v>
+        <v>0.0894067744774166</v>
       </c>
       <c r="C13">
-        <v>33.65707527188912</v>
+        <v>33.12958236998178</v>
       </c>
       <c r="D13">
-        <v>37.90607527188912</v>
+        <v>37.78258236998177</v>
       </c>
       <c r="E13">
-        <v>-19.456</v>
+        <v>-19.052</v>
       </c>
       <c r="F13">
-        <v>4.444</v>
+        <v>4.848</v>
       </c>
       <c r="G13">
         <v>0.195</v>
@@ -2347,45 +2347,45 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M13">
-        <v>0.2724172</v>
+        <v>0.3107568</v>
       </c>
       <c r="N13">
-        <v>0.7142494666666668</v>
+        <v>0.6759098666666667</v>
       </c>
       <c r="O13">
-        <v>0.1785623666666667</v>
+        <v>0.1689774666666667</v>
       </c>
       <c r="P13">
-        <v>0.5356871000000001</v>
+        <v>0.5069324000000001</v>
       </c>
       <c r="Q13">
-        <v>2.5156871</v>
+        <v>2.4869324</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.09461512299234061</v>
+        <v>0.09504292554251886</v>
       </c>
       <c r="T13">
-        <v>0.7551544276220306</v>
+        <v>0.7617723970157735</v>
       </c>
       <c r="U13">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V13">
         <v>0.25</v>
       </c>
       <c r="W13">
-        <v>0.045975</v>
+        <v>0.04807500000000001</v>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y13">
-        <v>3.621895631651256</v>
+        <v>3.175044493528916</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.0894067744774166</v>
+        <v>0.09007833949165006</v>
       </c>
       <c r="C14">
-        <v>33.12958236998178</v>
+        <v>32.15253783492511</v>
       </c>
       <c r="D14">
-        <v>37.78258236998177</v>
+        <v>37.20953783492511</v>
       </c>
       <c r="E14">
-        <v>-19.052</v>
+        <v>-18.648</v>
       </c>
       <c r="F14">
-        <v>4.848</v>
+        <v>5.252</v>
       </c>
       <c r="G14">
         <v>0.195</v>
@@ -2429,45 +2429,45 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M14">
-        <v>0.3107568</v>
+        <v>0.3776188</v>
       </c>
       <c r="N14">
-        <v>0.6759098666666667</v>
+        <v>0.6090478666666668</v>
       </c>
       <c r="O14">
-        <v>0.1689774666666667</v>
+        <v>0.1522619666666667</v>
       </c>
       <c r="P14">
-        <v>0.5069324000000001</v>
+        <v>0.4567859000000001</v>
       </c>
       <c r="Q14">
-        <v>2.4869324</v>
+        <v>2.4367859</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.09504292554251886</v>
+        <v>0.09548056263408053</v>
       </c>
       <c r="T14">
-        <v>0.7617723970157735</v>
+        <v>0.7685425036369588</v>
       </c>
       <c r="U14">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V14">
         <v>0.25</v>
       </c>
       <c r="W14">
-        <v>0.04807500000000001</v>
+        <v>0.053925</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y14">
-        <v>3.175044493528916</v>
+        <v>2.61286426064239</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09007833949165006</v>
+        <v>0.09045740450588352</v>
       </c>
       <c r="C15">
-        <v>32.15253783492511</v>
+        <v>31.43269247523435</v>
       </c>
       <c r="D15">
-        <v>37.20953783492511</v>
+        <v>36.89369247523435</v>
       </c>
       <c r="E15">
-        <v>-18.648</v>
+        <v>-18.244</v>
       </c>
       <c r="F15">
-        <v>5.252</v>
+        <v>5.656000000000001</v>
       </c>
       <c r="G15">
         <v>0.195</v>
@@ -2511,45 +2511,45 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M15">
-        <v>0.3776188</v>
+        <v>0.4287248000000001</v>
       </c>
       <c r="N15">
-        <v>0.6090478666666668</v>
+        <v>0.5579418666666667</v>
       </c>
       <c r="O15">
-        <v>0.1522619666666667</v>
+        <v>0.1394854666666667</v>
       </c>
       <c r="P15">
-        <v>0.4567859000000001</v>
+        <v>0.4184564</v>
       </c>
       <c r="Q15">
-        <v>2.4367859</v>
+        <v>2.3984564</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.09548056263408053</v>
+        <v>0.09592837733242271</v>
       </c>
       <c r="T15">
-        <v>0.7685425036369588</v>
+        <v>0.7754700545981718</v>
       </c>
       <c r="U15">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V15">
         <v>0.25</v>
       </c>
       <c r="W15">
-        <v>0.053925</v>
+        <v>0.05685</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y15">
-        <v>2.61286426064239</v>
+        <v>2.301398628366417</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09045740450588352</v>
+        <v>0.090456219520117</v>
       </c>
       <c r="C16">
-        <v>31.43269247523435</v>
+        <v>31.02967147661261</v>
       </c>
       <c r="D16">
-        <v>36.89369247523435</v>
+        <v>36.89467147661261</v>
       </c>
       <c r="E16">
-        <v>-18.244</v>
+        <v>-17.84</v>
       </c>
       <c r="F16">
-        <v>5.656000000000001</v>
+        <v>6.06</v>
       </c>
       <c r="G16">
         <v>0.195</v>
@@ -2593,28 +2593,28 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M16">
-        <v>0.4287248000000001</v>
+        <v>0.4593480000000001</v>
       </c>
       <c r="N16">
-        <v>0.5579418666666667</v>
+        <v>0.5273186666666667</v>
       </c>
       <c r="O16">
-        <v>0.1394854666666667</v>
+        <v>0.1318296666666667</v>
       </c>
       <c r="P16">
-        <v>0.4184564</v>
+        <v>0.395489</v>
       </c>
       <c r="Q16">
-        <v>2.3984564</v>
+        <v>2.375489</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.09592837733242271</v>
+        <v>0.09638672884719646</v>
       </c>
       <c r="T16">
-        <v>0.7754700545981718</v>
+        <v>0.7825606067584719</v>
       </c>
       <c r="U16">
         <v>0.07580000000000001</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>2.301398628366417</v>
+        <v>2.14797205314199</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09045621952011698</v>
+        <v>0.09045503453435044</v>
       </c>
       <c r="C17">
-        <v>31.02967147661262</v>
+        <v>30.62665052994931</v>
       </c>
       <c r="D17">
-        <v>36.89467147661261</v>
+        <v>36.89565052994931</v>
       </c>
       <c r="E17">
-        <v>-17.84</v>
+        <v>-17.436</v>
       </c>
       <c r="F17">
-        <v>6.06</v>
+        <v>6.464</v>
       </c>
       <c r="G17">
         <v>0.195</v>
@@ -2675,28 +2675,28 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M17">
-        <v>0.459348</v>
+        <v>0.4899712</v>
       </c>
       <c r="N17">
-        <v>0.5273186666666667</v>
+        <v>0.4966954666666668</v>
       </c>
       <c r="O17">
-        <v>0.1318296666666667</v>
+        <v>0.1241738666666667</v>
       </c>
       <c r="P17">
-        <v>0.395489</v>
+        <v>0.3725216000000001</v>
       </c>
       <c r="Q17">
-        <v>2.375489</v>
+        <v>2.3525216</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.09638672884719646</v>
+        <v>0.09685599349327434</v>
       </c>
       <c r="T17">
-        <v>0.7825606067584719</v>
+        <v>0.7898199815892555</v>
       </c>
       <c r="U17">
         <v>0.07580000000000001</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>2.14797205314199</v>
+        <v>2.013723799820616</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09045503453435044</v>
+        <v>0.09226434954858391</v>
       </c>
       <c r="C18">
-        <v>30.62665052994931</v>
+        <v>28.78593926395069</v>
       </c>
       <c r="D18">
-        <v>36.89565052994931</v>
+        <v>35.45893926395069</v>
       </c>
       <c r="E18">
-        <v>-17.436</v>
+        <v>-17.032</v>
       </c>
       <c r="F18">
-        <v>6.464</v>
+        <v>6.868</v>
       </c>
       <c r="G18">
         <v>0.195</v>
@@ -2757,45 +2757,45 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M18">
-        <v>0.4899712</v>
+        <v>0.61812</v>
       </c>
       <c r="N18">
-        <v>0.4966954666666668</v>
+        <v>0.3685466666666668</v>
       </c>
       <c r="O18">
-        <v>0.1241738666666667</v>
+        <v>0.0921366666666667</v>
       </c>
       <c r="P18">
-        <v>0.3725216000000001</v>
+        <v>0.2764100000000001</v>
       </c>
       <c r="Q18">
-        <v>2.3525216</v>
+        <v>2.25641</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.09685599349327434</v>
+        <v>0.09733656572118544</v>
       </c>
       <c r="T18">
-        <v>0.7898199815892555</v>
+        <v>0.7972542811147569</v>
       </c>
       <c r="U18">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V18">
         <v>0.25</v>
       </c>
       <c r="W18">
-        <v>0.05685</v>
+        <v>0.0675</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y18">
-        <v>2.013723799820616</v>
+        <v>1.596238055178067</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.09226434954858391</v>
+        <v>0.09236966456281737</v>
       </c>
       <c r="C19">
-        <v>28.78593926395069</v>
+        <v>28.30175061049263</v>
       </c>
       <c r="D19">
-        <v>35.45893926395069</v>
+        <v>35.37875061049262</v>
       </c>
       <c r="E19">
-        <v>-17.032</v>
+        <v>-16.628</v>
       </c>
       <c r="F19">
-        <v>6.868</v>
+        <v>7.272</v>
       </c>
       <c r="G19">
         <v>0.195</v>
@@ -2839,28 +2839,28 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M19">
-        <v>0.61812</v>
+        <v>0.65448</v>
       </c>
       <c r="N19">
-        <v>0.3685466666666668</v>
+        <v>0.3321866666666669</v>
       </c>
       <c r="O19">
-        <v>0.0921366666666667</v>
+        <v>0.08304666666666671</v>
       </c>
       <c r="P19">
-        <v>0.2764100000000001</v>
+        <v>0.2491400000000001</v>
       </c>
       <c r="Q19">
-        <v>2.25641</v>
+        <v>2.22914</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.09733656572118544</v>
+        <v>0.09782885922294801</v>
       </c>
       <c r="T19">
-        <v>0.7972542811147569</v>
+        <v>0.8048699050189289</v>
       </c>
       <c r="U19">
         <v>0.09</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>1.596238055178067</v>
+        <v>1.50755816322373</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09236966456281737</v>
+        <v>0.101700331896492</v>
       </c>
       <c r="C20">
-        <v>28.30175061049263</v>
+        <v>21.9924663048683</v>
       </c>
       <c r="D20">
-        <v>35.37875061049262</v>
+        <v>29.4734663048683</v>
       </c>
       <c r="E20">
-        <v>-16.628</v>
+        <v>-16.224</v>
       </c>
       <c r="F20">
-        <v>7.271999999999999</v>
+        <v>7.676</v>
       </c>
       <c r="G20">
         <v>0.195</v>
@@ -2921,45 +2921,45 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M20">
-        <v>0.65448</v>
+        <v>1.1268368</v>
       </c>
       <c r="N20">
-        <v>0.3321866666666669</v>
+        <v>-0.1401701333333334</v>
       </c>
       <c r="O20">
-        <v>0.08304666666666671</v>
+        <v>-0.03504253333333335</v>
       </c>
       <c r="P20">
-        <v>0.2491400000000001</v>
+        <v>-0.1051276</v>
       </c>
       <c r="Q20">
-        <v>2.22914</v>
+        <v>1.8748724</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.09782885922294801</v>
+        <v>0.09865918821919518</v>
       </c>
       <c r="T20">
-        <v>0.8048699050189289</v>
+        <v>0.8177148305146075</v>
       </c>
       <c r="U20">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V20">
-        <v>0.25</v>
+        <v>0.2189018557671055</v>
       </c>
       <c r="W20">
-        <v>0.0675</v>
+        <v>0.1146652075733889</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y20">
-        <v>1.50755816322373</v>
+        <v>0.8756074230684219</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.101700331896492</v>
+        <v>0.102710331896492</v>
       </c>
       <c r="C21">
-        <v>21.9924663048683</v>
+        <v>21.06539430764187</v>
       </c>
       <c r="D21">
-        <v>29.4734663048683</v>
+        <v>28.95039430764187</v>
       </c>
       <c r="E21">
-        <v>-16.224</v>
+        <v>-15.82</v>
       </c>
       <c r="F21">
-        <v>7.676</v>
+        <v>8.08</v>
       </c>
       <c r="G21">
         <v>0.195</v>
@@ -3003,37 +3003,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M21">
-        <v>1.1268368</v>
+        <v>1.186144</v>
       </c>
       <c r="N21">
-        <v>-0.1401701333333334</v>
+        <v>-0.1994773333333333</v>
       </c>
       <c r="O21">
-        <v>-0.03504253333333335</v>
+        <v>-0.04986933333333332</v>
       </c>
       <c r="P21">
-        <v>-0.1051276</v>
+        <v>-0.149608</v>
       </c>
       <c r="Q21">
-        <v>1.8748724</v>
+        <v>1.830392</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.09865918821919518</v>
+        <v>0.09931992807193513</v>
       </c>
       <c r="T21">
-        <v>0.8177148305146075</v>
+        <v>0.8279362658960401</v>
       </c>
       <c r="U21">
         <v>0.1468</v>
       </c>
       <c r="V21">
-        <v>0.2189018557671055</v>
+        <v>0.2079567629787502</v>
       </c>
       <c r="W21">
-        <v>0.1146652075733889</v>
+        <v>0.1162719471947195</v>
       </c>
       <c r="X21" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>0.8756074230684219</v>
+        <v>0.8318270519150008</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.102710331896492</v>
+        <v>0.1155600071945479</v>
       </c>
       <c r="C22">
-        <v>21.06539430764187</v>
+        <v>15.32878065743919</v>
       </c>
       <c r="D22">
-        <v>28.95039430764187</v>
+        <v>23.61778065743919</v>
       </c>
       <c r="E22">
-        <v>-15.82</v>
+        <v>-15.416</v>
       </c>
       <c r="F22">
-        <v>8.08</v>
+        <v>8.484</v>
       </c>
       <c r="G22">
         <v>0.195</v>
@@ -3085,45 +3085,45 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M22">
-        <v>1.186144</v>
+        <v>1.7035872</v>
       </c>
       <c r="N22">
-        <v>-0.1994773333333333</v>
+        <v>-0.7169205333333333</v>
       </c>
       <c r="O22">
-        <v>-0.04986933333333332</v>
+        <v>-0.1792301333333333</v>
       </c>
       <c r="P22">
-        <v>-0.149608</v>
+        <v>-0.5376904</v>
       </c>
       <c r="Q22">
-        <v>1.830392</v>
+        <v>1.4423096</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.09931992807193513</v>
+        <v>0.1006298958931696</v>
       </c>
       <c r="T22">
-        <v>0.8279362658960401</v>
+        <v>0.8482010514708462</v>
       </c>
       <c r="U22">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V22">
-        <v>0.2079567629787502</v>
+        <v>0.1447925099852046</v>
       </c>
       <c r="W22">
-        <v>0.1162719471947195</v>
+        <v>0.1717256639949709</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y22">
-        <v>0.8318270519150008</v>
+        <v>0.5791700399408183</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1155600071945479</v>
+        <v>0.1171100071945478</v>
       </c>
       <c r="C23">
-        <v>15.32878065743919</v>
+        <v>14.41142269466186</v>
       </c>
       <c r="D23">
-        <v>23.61778065743919</v>
+        <v>23.10442269466186</v>
       </c>
       <c r="E23">
-        <v>-15.416</v>
+        <v>-15.012</v>
       </c>
       <c r="F23">
-        <v>8.484</v>
+        <v>8.888</v>
       </c>
       <c r="G23">
         <v>0.195</v>
@@ -3167,37 +3167,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M23">
-        <v>1.7035872</v>
+        <v>1.7847104</v>
       </c>
       <c r="N23">
-        <v>-0.7169205333333333</v>
+        <v>-0.7980437333333332</v>
       </c>
       <c r="O23">
-        <v>-0.1792301333333333</v>
+        <v>-0.1995109333333333</v>
       </c>
       <c r="P23">
-        <v>-0.5376904</v>
+        <v>-0.5985327999999999</v>
       </c>
       <c r="Q23">
-        <v>1.4423096</v>
+        <v>1.3814672</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1006298958931696</v>
+        <v>0.1013328432764153</v>
       </c>
       <c r="T23">
-        <v>0.8482010514708462</v>
+        <v>0.8590754239256005</v>
       </c>
       <c r="U23">
         <v>0.2008</v>
       </c>
       <c r="V23">
-        <v>0.1447925099852046</v>
+        <v>0.1382110322586044</v>
       </c>
       <c r="W23">
-        <v>0.1717256639949709</v>
+        <v>0.1730472247224722</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>0.5791700399408183</v>
+        <v>0.5528441290344175</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1171100071945478</v>
+        <v>0.1186600071945478</v>
       </c>
       <c r="C24">
-        <v>14.41142269466186</v>
+        <v>13.51590675120193</v>
       </c>
       <c r="D24">
-        <v>23.10442269466186</v>
+        <v>22.61290675120193</v>
       </c>
       <c r="E24">
-        <v>-15.012</v>
+        <v>-14.608</v>
       </c>
       <c r="F24">
-        <v>8.888</v>
+        <v>9.292</v>
       </c>
       <c r="G24">
         <v>0.195</v>
@@ -3249,37 +3249,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M24">
-        <v>1.7847104</v>
+        <v>1.8658336</v>
       </c>
       <c r="N24">
-        <v>-0.7980437333333332</v>
+        <v>-0.8791669333333332</v>
       </c>
       <c r="O24">
-        <v>-0.1995109333333333</v>
+        <v>-0.2197917333333333</v>
       </c>
       <c r="P24">
-        <v>-0.5985327999999999</v>
+        <v>-0.6593751999999999</v>
       </c>
       <c r="Q24">
-        <v>1.3814672</v>
+        <v>1.3206248</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1013328432764153</v>
+        <v>0.1020540490332519</v>
       </c>
       <c r="T24">
-        <v>0.8590754239256005</v>
+        <v>0.8702322476129459</v>
       </c>
       <c r="U24">
         <v>0.2008</v>
       </c>
       <c r="V24">
-        <v>0.1382110322586044</v>
+        <v>0.1322018569430129</v>
       </c>
       <c r="W24">
-        <v>0.1730472247224722</v>
+        <v>0.174253867125843</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>0.5528441290344175</v>
+        <v>0.5288074277720515</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1186600071945478</v>
+        <v>0.1202100071945478</v>
       </c>
       <c r="C25">
-        <v>13.51590675120193</v>
+        <v>12.64086788444408</v>
       </c>
       <c r="D25">
-        <v>22.61290675120193</v>
+        <v>22.14186788444408</v>
       </c>
       <c r="E25">
-        <v>-14.608</v>
+        <v>-14.204</v>
       </c>
       <c r="F25">
-        <v>9.292</v>
+        <v>9.696</v>
       </c>
       <c r="G25">
         <v>0.195</v>
@@ -3331,37 +3331,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M25">
-        <v>1.8658336</v>
+        <v>1.9469568</v>
       </c>
       <c r="N25">
-        <v>-0.8791669333333332</v>
+        <v>-0.9602901333333331</v>
       </c>
       <c r="O25">
-        <v>-0.2197917333333333</v>
+        <v>-0.2400725333333333</v>
       </c>
       <c r="P25">
-        <v>-0.6593751999999999</v>
+        <v>-0.7202175999999998</v>
       </c>
       <c r="Q25">
-        <v>1.3206248</v>
+        <v>1.2597824</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1020540490332519</v>
+        <v>0.1027942338889526</v>
       </c>
       <c r="T25">
-        <v>0.8702322476129459</v>
+        <v>0.8816826719236427</v>
       </c>
       <c r="U25">
         <v>0.2008</v>
       </c>
       <c r="V25">
-        <v>0.1322018569430129</v>
+        <v>0.126693446237054</v>
       </c>
       <c r="W25">
-        <v>0.174253867125843</v>
+        <v>0.1753599559955996</v>
       </c>
       <c r="X25" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>0.5288074277720515</v>
+        <v>0.506773784948216</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1202100071945478</v>
+        <v>0.1307116322127217</v>
       </c>
       <c r="C26">
-        <v>12.64086788444408</v>
+        <v>9.498425722104626</v>
       </c>
       <c r="D26">
-        <v>22.14186788444408</v>
+        <v>19.40342572210463</v>
       </c>
       <c r="E26">
-        <v>-14.204</v>
+        <v>-13.8</v>
       </c>
       <c r="F26">
-        <v>9.696</v>
+        <v>10.1</v>
       </c>
       <c r="G26">
         <v>0.195</v>
@@ -3413,45 +3413,45 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M26">
-        <v>1.9469568</v>
+        <v>2.38158</v>
       </c>
       <c r="N26">
-        <v>-0.9602901333333331</v>
+        <v>-1.394913333333333</v>
       </c>
       <c r="O26">
-        <v>-0.2400725333333333</v>
+        <v>-0.3487283333333333</v>
       </c>
       <c r="P26">
-        <v>-0.7202175999999998</v>
+        <v>-1.046185</v>
       </c>
       <c r="Q26">
-        <v>1.2597824</v>
+        <v>0.9338150000000001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1027942338889526</v>
+        <v>0.103822990365037</v>
       </c>
       <c r="T26">
-        <v>0.8816826719236427</v>
+        <v>0.8975972074249038</v>
       </c>
       <c r="U26">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V26">
-        <v>0.126693446237054</v>
+        <v>0.1035726982367448</v>
       </c>
       <c r="W26">
-        <v>0.1753599559955996</v>
+        <v>0.2113775577557756</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y26">
-        <v>0.506773784948216</v>
+        <v>0.4142907929469792</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1307116322127217</v>
+        <v>0.1326116322127217</v>
       </c>
       <c r="C27">
-        <v>9.498425722104626</v>
+        <v>8.669753268283438</v>
       </c>
       <c r="D27">
-        <v>19.40342572210463</v>
+        <v>18.97875326828344</v>
       </c>
       <c r="E27">
-        <v>-13.8</v>
+        <v>-13.396</v>
       </c>
       <c r="F27">
-        <v>10.1</v>
+        <v>10.504</v>
       </c>
       <c r="G27">
         <v>0.195</v>
@@ -3495,37 +3495,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M27">
-        <v>2.38158</v>
+        <v>2.4768432</v>
       </c>
       <c r="N27">
-        <v>-1.394913333333333</v>
+        <v>-1.490176533333333</v>
       </c>
       <c r="O27">
-        <v>-0.3487283333333333</v>
+        <v>-0.3725441333333332</v>
       </c>
       <c r="P27">
-        <v>-1.046185</v>
+        <v>-1.1176324</v>
       </c>
       <c r="Q27">
-        <v>0.9338150000000001</v>
+        <v>0.8623676000000002</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.103822990365037</v>
+        <v>0.1046070848294294</v>
       </c>
       <c r="T27">
-        <v>0.8975972074249038</v>
+        <v>0.9097268994171321</v>
       </c>
       <c r="U27">
         <v>0.2358</v>
       </c>
       <c r="V27">
-        <v>0.1035726982367448</v>
+        <v>0.09958913291994693</v>
       </c>
       <c r="W27">
-        <v>0.2113775577557756</v>
+        <v>0.2123168824574765</v>
       </c>
       <c r="X27" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>0.4142907929469792</v>
+        <v>0.3983565316797878</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1326116322127217</v>
+        <v>0.1345116322127217</v>
       </c>
       <c r="C28">
-        <v>8.669753268283438</v>
+        <v>7.859271837265792</v>
       </c>
       <c r="D28">
-        <v>18.97875326828344</v>
+        <v>18.57227183726579</v>
       </c>
       <c r="E28">
-        <v>-13.396</v>
+        <v>-12.992</v>
       </c>
       <c r="F28">
-        <v>10.504</v>
+        <v>10.908</v>
       </c>
       <c r="G28">
         <v>0.195</v>
@@ -3577,37 +3577,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M28">
-        <v>2.4768432</v>
+        <v>2.5721064</v>
       </c>
       <c r="N28">
-        <v>-1.490176533333333</v>
+        <v>-1.585439733333333</v>
       </c>
       <c r="O28">
-        <v>-0.3725441333333332</v>
+        <v>-0.3963599333333333</v>
       </c>
       <c r="P28">
-        <v>-1.1176324</v>
+        <v>-1.1890798</v>
       </c>
       <c r="Q28">
-        <v>0.8623676000000002</v>
+        <v>0.7909202</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1046070848294294</v>
+        <v>0.1054126613339422</v>
       </c>
       <c r="T28">
-        <v>0.9097268994171321</v>
+        <v>0.9221889117379147</v>
       </c>
       <c r="U28">
         <v>0.2358</v>
       </c>
       <c r="V28">
-        <v>0.09958913291994693</v>
+        <v>0.09590064651550445</v>
       </c>
       <c r="W28">
-        <v>0.2123168824574765</v>
+        <v>0.2131866275516441</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>0.3983565316797878</v>
+        <v>0.3836025860620178</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1345116322127217</v>
+        <v>0.1364116322127217</v>
       </c>
       <c r="C29">
-        <v>7.859271837265792</v>
+        <v>7.065837107650015</v>
       </c>
       <c r="D29">
-        <v>18.57227183726579</v>
+        <v>18.18283710765002</v>
       </c>
       <c r="E29">
-        <v>-12.992</v>
+        <v>-12.588</v>
       </c>
       <c r="F29">
-        <v>10.908</v>
+        <v>11.312</v>
       </c>
       <c r="G29">
         <v>0.195</v>
@@ -3659,37 +3659,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M29">
-        <v>2.5721064</v>
+        <v>2.6673696</v>
       </c>
       <c r="N29">
-        <v>-1.585439733333333</v>
+        <v>-1.680702933333333</v>
       </c>
       <c r="O29">
-        <v>-0.3963599333333333</v>
+        <v>-0.4201757333333334</v>
       </c>
       <c r="P29">
-        <v>-1.1890798</v>
+        <v>-1.2605272</v>
       </c>
       <c r="Q29">
-        <v>0.7909202</v>
+        <v>0.7194727999999999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1054126613339422</v>
+        <v>0.1062406149635803</v>
       </c>
       <c r="T29">
-        <v>0.9221889117379147</v>
+        <v>0.9349970910676081</v>
       </c>
       <c r="U29">
         <v>0.2358</v>
       </c>
       <c r="V29">
-        <v>0.09590064651550445</v>
+        <v>0.092475623425665</v>
       </c>
       <c r="W29">
-        <v>0.2131866275516441</v>
+        <v>0.2139942479962282</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>0.3836025860620178</v>
+        <v>0.36990249370266</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1364116322127217</v>
+        <v>0.1383116322127217</v>
       </c>
       <c r="C30">
-        <v>7.065837107650015</v>
+        <v>6.28839876613317</v>
       </c>
       <c r="D30">
-        <v>18.18283710765002</v>
+        <v>17.80939876613317</v>
       </c>
       <c r="E30">
-        <v>-12.588</v>
+        <v>-12.184</v>
       </c>
       <c r="F30">
-        <v>11.312</v>
+        <v>11.716</v>
       </c>
       <c r="G30">
         <v>0.195</v>
@@ -3741,37 +3741,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M30">
-        <v>2.6673696</v>
+        <v>2.7626328</v>
       </c>
       <c r="N30">
-        <v>-1.680702933333333</v>
+        <v>-1.775966133333334</v>
       </c>
       <c r="O30">
-        <v>-0.4201757333333334</v>
+        <v>-0.4439915333333334</v>
       </c>
       <c r="P30">
-        <v>-1.2605272</v>
+        <v>-1.3319746</v>
       </c>
       <c r="Q30">
-        <v>0.7194727999999999</v>
+        <v>0.6480253999999999</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1062406149635803</v>
+        <v>0.1070918912306729</v>
       </c>
       <c r="T30">
-        <v>0.9349970910676081</v>
+        <v>0.9481660641812364</v>
       </c>
       <c r="U30">
         <v>0.2358</v>
       </c>
       <c r="V30">
-        <v>0.092475623425665</v>
+        <v>0.08928680882477999</v>
       </c>
       <c r="W30">
-        <v>0.2139942479962282</v>
+        <v>0.2147461704791169</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>0.36990249370266</v>
+        <v>0.35714723529912</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1383116322127217</v>
+        <v>0.1402116322127217</v>
       </c>
       <c r="C31">
-        <v>6.288398766133179</v>
+        <v>5.525991048115847</v>
       </c>
       <c r="D31">
-        <v>17.80939876613318</v>
+        <v>17.45099104811585</v>
       </c>
       <c r="E31">
-        <v>-12.184</v>
+        <v>-11.78</v>
       </c>
       <c r="F31">
-        <v>11.716</v>
+        <v>12.12</v>
       </c>
       <c r="G31">
         <v>0.195</v>
@@ -3823,37 +3823,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M31">
-        <v>2.7626328</v>
+        <v>2.857896</v>
       </c>
       <c r="N31">
-        <v>-1.775966133333333</v>
+        <v>-1.871229333333333</v>
       </c>
       <c r="O31">
-        <v>-0.4439915333333333</v>
+        <v>-0.4678073333333332</v>
       </c>
       <c r="P31">
-        <v>-1.3319746</v>
+        <v>-1.403422</v>
       </c>
       <c r="Q31">
-        <v>0.6480254000000001</v>
+        <v>0.5765780000000003</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1070918912306729</v>
+        <v>0.1079674896768254</v>
       </c>
       <c r="T31">
-        <v>0.9481660641812364</v>
+        <v>0.9617112936695397</v>
       </c>
       <c r="U31">
         <v>0.2358</v>
       </c>
       <c r="V31">
-        <v>0.08928680882478</v>
+        <v>0.08631058186395402</v>
       </c>
       <c r="W31">
-        <v>0.2147461704791169</v>
+        <v>0.2154479647964797</v>
       </c>
       <c r="X31" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>0.3571472352991201</v>
+        <v>0.3452423274558161</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1402116322127217</v>
+        <v>0.1421116322127217</v>
       </c>
       <c r="C32">
-        <v>5.525991048115847</v>
+        <v>4.777724397975531</v>
       </c>
       <c r="D32">
-        <v>17.45099104811585</v>
+        <v>17.10672439797553</v>
       </c>
       <c r="E32">
-        <v>-11.78</v>
+        <v>-11.376</v>
       </c>
       <c r="F32">
-        <v>12.12</v>
+        <v>12.524</v>
       </c>
       <c r="G32">
         <v>0.195</v>
@@ -3905,37 +3905,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M32">
-        <v>2.857896</v>
+        <v>2.9531592</v>
       </c>
       <c r="N32">
-        <v>-1.871229333333333</v>
+        <v>-1.966492533333333</v>
       </c>
       <c r="O32">
-        <v>-0.4678073333333332</v>
+        <v>-0.4916231333333333</v>
       </c>
       <c r="P32">
-        <v>-1.403422</v>
+        <v>-1.4748694</v>
       </c>
       <c r="Q32">
-        <v>0.5765780000000003</v>
+        <v>0.5051306000000002</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1079674896768254</v>
+        <v>0.1088684677880837</v>
       </c>
       <c r="T32">
-        <v>0.9617112936695397</v>
+        <v>0.9756491385053301</v>
       </c>
       <c r="U32">
         <v>0.2358</v>
       </c>
       <c r="V32">
-        <v>0.08631058186395402</v>
+        <v>0.08352636954576194</v>
       </c>
       <c r="W32">
-        <v>0.2154479647964797</v>
+        <v>0.2161044820611093</v>
       </c>
       <c r="X32" t="inlineStr">
         <is>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>0.3452423274558161</v>
+        <v>0.3341054781830478</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1421116322127217</v>
+        <v>0.1440116322127217</v>
       </c>
       <c r="C33">
-        <v>4.777724397975531</v>
+        <v>4.042778097380973</v>
       </c>
       <c r="D33">
-        <v>17.10672439797553</v>
+        <v>16.77577809738097</v>
       </c>
       <c r="E33">
-        <v>-11.376</v>
+        <v>-10.972</v>
       </c>
       <c r="F33">
-        <v>12.524</v>
+        <v>12.928</v>
       </c>
       <c r="G33">
         <v>0.195</v>
@@ -3987,37 +3987,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M33">
-        <v>2.9531592</v>
+        <v>3.0484224</v>
       </c>
       <c r="N33">
-        <v>-1.966492533333333</v>
+        <v>-2.061755733333333</v>
       </c>
       <c r="O33">
-        <v>-0.4916231333333333</v>
+        <v>-0.5154389333333332</v>
       </c>
       <c r="P33">
-        <v>-1.4748694</v>
+        <v>-1.5463168</v>
       </c>
       <c r="Q33">
-        <v>0.5051306000000002</v>
+        <v>0.4336832000000004</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1088684677880837</v>
+        <v>0.1097959452555556</v>
       </c>
       <c r="T33">
-        <v>0.9756491385053301</v>
+        <v>0.989996919953938</v>
       </c>
       <c r="U33">
         <v>0.2358</v>
       </c>
       <c r="V33">
-        <v>0.08352636954576194</v>
+        <v>0.08091617049745689</v>
       </c>
       <c r="W33">
-        <v>0.2161044820611093</v>
+        <v>0.2167199669966997</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>0.3341054781830478</v>
+        <v>0.3236646819898276</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1440116322127217</v>
+        <v>0.1459116322127217</v>
       </c>
       <c r="C34">
-        <v>4.042778097380973</v>
+        <v>3.320393733041598</v>
       </c>
       <c r="D34">
-        <v>16.77577809738097</v>
+        <v>16.4573937330416</v>
       </c>
       <c r="E34">
-        <v>-10.972</v>
+        <v>-10.568</v>
       </c>
       <c r="F34">
-        <v>12.928</v>
+        <v>13.332</v>
       </c>
       <c r="G34">
         <v>0.195</v>
@@ -4069,37 +4069,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M34">
-        <v>3.0484224</v>
+        <v>3.1436856</v>
       </c>
       <c r="N34">
-        <v>-2.061755733333333</v>
+        <v>-2.157018933333334</v>
       </c>
       <c r="O34">
-        <v>-0.5154389333333332</v>
+        <v>-0.5392547333333334</v>
       </c>
       <c r="P34">
-        <v>-1.5463168</v>
+        <v>-1.6177642</v>
       </c>
       <c r="Q34">
-        <v>0.4336832000000004</v>
+        <v>0.3622357999999997</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1097959452555556</v>
+        <v>0.1107511086175788</v>
       </c>
       <c r="T34">
-        <v>0.989996919953938</v>
+        <v>1.004772993386086</v>
       </c>
       <c r="U34">
         <v>0.2358</v>
       </c>
       <c r="V34">
-        <v>0.08091617049745689</v>
+        <v>0.07846416533086727</v>
       </c>
       <c r="W34">
-        <v>0.2167199669966997</v>
+        <v>0.2172981498149815</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>0.3236646819898276</v>
+        <v>0.3138566613234691</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1459116322127217</v>
+        <v>0.1478116322127217</v>
       </c>
       <c r="C35">
-        <v>3.320393733041598</v>
+        <v>2.609869394448776</v>
       </c>
       <c r="D35">
-        <v>16.4573937330416</v>
+        <v>16.15086939444878</v>
       </c>
       <c r="E35">
-        <v>-10.568</v>
+        <v>-10.164</v>
       </c>
       <c r="F35">
-        <v>13.332</v>
+        <v>13.736</v>
       </c>
       <c r="G35">
         <v>0.195</v>
@@ -4151,37 +4151,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M35">
-        <v>3.1436856</v>
+        <v>3.2389488</v>
       </c>
       <c r="N35">
-        <v>-2.157018933333334</v>
+        <v>-2.252282133333333</v>
       </c>
       <c r="O35">
-        <v>-0.5392547333333334</v>
+        <v>-0.5630705333333333</v>
       </c>
       <c r="P35">
-        <v>-1.6177642</v>
+        <v>-1.6892116</v>
       </c>
       <c r="Q35">
-        <v>0.3622357999999997</v>
+        <v>0.2907883999999998</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1107511086175788</v>
+        <v>0.1117352163239057</v>
       </c>
       <c r="T35">
-        <v>1.004772993386086</v>
+        <v>1.019996826619209</v>
       </c>
       <c r="U35">
         <v>0.2358</v>
       </c>
       <c r="V35">
-        <v>0.07846416533086727</v>
+        <v>0.07615639576231235</v>
       </c>
       <c r="W35">
-        <v>0.2172981498149815</v>
+        <v>0.2178423218792468</v>
       </c>
       <c r="X35" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.3138566613234691</v>
+        <v>0.3046255830492495</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1478116322127217</v>
+        <v>0.1497116322127217</v>
       </c>
       <c r="C36">
-        <v>2.609869394448776</v>
+        <v>1.910554508174705</v>
       </c>
       <c r="D36">
-        <v>16.15086939444878</v>
+        <v>15.85555450817471</v>
       </c>
       <c r="E36">
-        <v>-10.164</v>
+        <v>-9.759999999999998</v>
       </c>
       <c r="F36">
-        <v>13.736</v>
+        <v>14.14</v>
       </c>
       <c r="G36">
         <v>0.195</v>
@@ -4233,37 +4233,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M36">
-        <v>3.2389488</v>
+        <v>3.334212</v>
       </c>
       <c r="N36">
-        <v>-2.252282133333333</v>
+        <v>-2.347545333333334</v>
       </c>
       <c r="O36">
-        <v>-0.5630705333333333</v>
+        <v>-0.5868863333333334</v>
       </c>
       <c r="P36">
-        <v>-1.6892116</v>
+        <v>-1.760659</v>
       </c>
       <c r="Q36">
-        <v>0.2907883999999998</v>
+        <v>0.2193409999999998</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1117352163239057</v>
+        <v>0.1127496042673505</v>
       </c>
       <c r="T36">
-        <v>1.019996826619209</v>
+        <v>1.035689085490274</v>
       </c>
       <c r="U36">
         <v>0.2358</v>
       </c>
       <c r="V36">
-        <v>0.07615639576231235</v>
+        <v>0.073980498740532</v>
       </c>
       <c r="W36">
-        <v>0.2178423218792468</v>
+        <v>0.2183553983969826</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
@@ -4271,7 +4271,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.3046255830492495</v>
+        <v>0.295921994962128</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1497116322127217</v>
+        <v>0.1516116322127217</v>
       </c>
       <c r="C37">
-        <v>1.910554508174705</v>
+        <v>1.221845228716962</v>
       </c>
       <c r="D37">
-        <v>15.85555450817471</v>
+        <v>15.57084522871696</v>
       </c>
       <c r="E37">
-        <v>-9.759999999999998</v>
+        <v>-9.355999999999998</v>
       </c>
       <c r="F37">
-        <v>14.14</v>
+        <v>14.544</v>
       </c>
       <c r="G37">
         <v>0.195</v>
@@ -4315,37 +4315,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M37">
-        <v>3.334212</v>
+        <v>3.4294752</v>
       </c>
       <c r="N37">
-        <v>-2.347545333333334</v>
+        <v>-2.442808533333333</v>
       </c>
       <c r="O37">
-        <v>-0.5868863333333334</v>
+        <v>-0.6107021333333333</v>
       </c>
       <c r="P37">
-        <v>-1.760659</v>
+        <v>-1.8321064</v>
       </c>
       <c r="Q37">
-        <v>0.2193409999999998</v>
+        <v>0.1478936</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1127496042673505</v>
+        <v>0.1137956918340278</v>
       </c>
       <c r="T37">
-        <v>1.035689085490274</v>
+        <v>1.051871727451059</v>
       </c>
       <c r="U37">
         <v>0.2358</v>
       </c>
       <c r="V37">
-        <v>0.073980498740532</v>
+        <v>0.07192548488662834</v>
       </c>
       <c r="W37">
-        <v>0.2183553983969826</v>
+        <v>0.2188399706637331</v>
       </c>
       <c r="X37" t="inlineStr">
         <is>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.295921994962128</v>
+        <v>0.2877019395465134</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1516116322127217</v>
+        <v>0.1535116322127217</v>
       </c>
       <c r="C38">
-        <v>1.221845228716964</v>
+        <v>0.5431803171674439</v>
       </c>
       <c r="D38">
-        <v>15.57084522871696</v>
+        <v>15.29618031716744</v>
       </c>
       <c r="E38">
-        <v>-9.356</v>
+        <v>-8.952</v>
       </c>
       <c r="F38">
-        <v>14.544</v>
+        <v>14.948</v>
       </c>
       <c r="G38">
         <v>0.195</v>
@@ -4397,37 +4397,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M38">
-        <v>3.4294752</v>
+        <v>3.5247384</v>
       </c>
       <c r="N38">
-        <v>-2.442808533333333</v>
+        <v>-2.538071733333333</v>
       </c>
       <c r="O38">
-        <v>-0.6107021333333332</v>
+        <v>-0.6345179333333333</v>
       </c>
       <c r="P38">
-        <v>-1.8321064</v>
+        <v>-1.9035538</v>
       </c>
       <c r="Q38">
-        <v>0.1478936000000002</v>
+        <v>0.07644620000000013</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1137956918340278</v>
+        <v>0.114874988529806</v>
       </c>
       <c r="T38">
-        <v>1.051871727451059</v>
+        <v>1.068568104077266</v>
       </c>
       <c r="U38">
         <v>0.2358</v>
       </c>
       <c r="V38">
-        <v>0.07192548488662834</v>
+        <v>0.06998155286266541</v>
       </c>
       <c r="W38">
-        <v>0.2188399706637331</v>
+        <v>0.2192983498349835</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>0.2877019395465134</v>
+        <v>0.2799262114506617</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1535116322127217</v>
+        <v>0.1554116322127217</v>
       </c>
       <c r="C39">
-        <v>0.5431803171674439</v>
+        <v>-0.1259625514855571</v>
       </c>
       <c r="D39">
-        <v>15.29618031716744</v>
+        <v>15.03103744851444</v>
       </c>
       <c r="E39">
-        <v>-8.952</v>
+        <v>-8.547999999999998</v>
       </c>
       <c r="F39">
-        <v>14.948</v>
+        <v>15.352</v>
       </c>
       <c r="G39">
         <v>0.195</v>
@@ -4479,37 +4479,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M39">
-        <v>3.5247384</v>
+        <v>3.6200016</v>
       </c>
       <c r="N39">
-        <v>-2.538071733333333</v>
+        <v>-2.633334933333333</v>
       </c>
       <c r="O39">
-        <v>-0.6345179333333333</v>
+        <v>-0.6583337333333333</v>
       </c>
       <c r="P39">
-        <v>-1.9035538</v>
+        <v>-1.9750012</v>
       </c>
       <c r="Q39">
-        <v>0.07644620000000013</v>
+        <v>0.004998800000000081</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.114874988529806</v>
+        <v>0.1159891012480287</v>
       </c>
       <c r="T39">
-        <v>1.068568104077266</v>
+        <v>1.085803073497867</v>
       </c>
       <c r="U39">
         <v>0.2358</v>
       </c>
       <c r="V39">
-        <v>0.06998155286266541</v>
+        <v>0.06813993305049</v>
       </c>
       <c r="W39">
-        <v>0.2192983498349835</v>
+        <v>0.2197326037866945</v>
       </c>
       <c r="X39" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.2799262114506617</v>
+        <v>0.2725597322019601</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1554116322127217</v>
+        <v>0.1573116322127217</v>
       </c>
       <c r="C40">
-        <v>-0.1259625514855571</v>
+        <v>-0.7860701035452227</v>
       </c>
       <c r="D40">
-        <v>15.03103744851444</v>
+        <v>14.77492989645478</v>
       </c>
       <c r="E40">
-        <v>-8.547999999999998</v>
+        <v>-8.143999999999998</v>
       </c>
       <c r="F40">
-        <v>15.352</v>
+        <v>15.756</v>
       </c>
       <c r="G40">
         <v>0.195</v>
@@ -4561,37 +4561,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M40">
-        <v>3.6200016</v>
+        <v>3.7152648</v>
       </c>
       <c r="N40">
-        <v>-2.633334933333333</v>
+        <v>-2.728598133333334</v>
       </c>
       <c r="O40">
-        <v>-0.6583337333333333</v>
+        <v>-0.6821495333333334</v>
       </c>
       <c r="P40">
-        <v>-1.9750012</v>
+        <v>-2.0464486</v>
       </c>
       <c r="Q40">
-        <v>0.004998800000000081</v>
+        <v>-0.06644860000000019</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1159891012480287</v>
+        <v>0.1171397422520947</v>
       </c>
       <c r="T40">
-        <v>1.085803073497867</v>
+        <v>1.103603123883078</v>
       </c>
       <c r="U40">
         <v>0.2358</v>
       </c>
       <c r="V40">
-        <v>0.06813993305049</v>
+        <v>0.06639275527996462</v>
       </c>
       <c r="W40">
-        <v>0.2197326037866945</v>
+        <v>0.2201445883049844</v>
       </c>
       <c r="X40" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.2725597322019601</v>
+        <v>0.2655710211198584</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1573116322127217</v>
+        <v>0.1592116322127217</v>
       </c>
       <c r="C41">
-        <v>-0.7860701035452227</v>
+        <v>-1.437596448555487</v>
       </c>
       <c r="D41">
-        <v>14.77492989645478</v>
+        <v>14.52740355144451</v>
       </c>
       <c r="E41">
-        <v>-8.143999999999998</v>
+        <v>-7.739999999999998</v>
       </c>
       <c r="F41">
-        <v>15.756</v>
+        <v>16.16</v>
       </c>
       <c r="G41">
         <v>0.195</v>
@@ -4643,37 +4643,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M41">
-        <v>3.7152648</v>
+        <v>3.810528</v>
       </c>
       <c r="N41">
-        <v>-2.728598133333334</v>
+        <v>-2.823861333333333</v>
       </c>
       <c r="O41">
-        <v>-0.6821495333333334</v>
+        <v>-0.7059653333333333</v>
       </c>
       <c r="P41">
-        <v>-2.0464486</v>
+        <v>-2.117896</v>
       </c>
       <c r="Q41">
-        <v>-0.06644860000000019</v>
+        <v>-0.137896</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1171397422520947</v>
+        <v>0.1183287379562963</v>
       </c>
       <c r="T41">
-        <v>1.103603123883078</v>
+        <v>1.12199650928113</v>
       </c>
       <c r="U41">
         <v>0.2358</v>
       </c>
       <c r="V41">
-        <v>0.06639275527996462</v>
+        <v>0.0647329363979655</v>
       </c>
       <c r="W41">
-        <v>0.2201445883049844</v>
+        <v>0.2205359735973597</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.2655710211198584</v>
+        <v>0.2589317455918621</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1592116322127217</v>
+        <v>0.1611116322127217</v>
       </c>
       <c r="C42">
-        <v>-1.437596448555487</v>
+        <v>-2.080965766447251</v>
       </c>
       <c r="D42">
-        <v>14.52740355144451</v>
+        <v>14.28803423355275</v>
       </c>
       <c r="E42">
-        <v>-7.739999999999998</v>
+        <v>-7.335999999999999</v>
       </c>
       <c r="F42">
-        <v>16.16</v>
+        <v>16.564</v>
       </c>
       <c r="G42">
         <v>0.195</v>
@@ -4725,37 +4725,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M42">
-        <v>3.810528</v>
+        <v>3.9057912</v>
       </c>
       <c r="N42">
-        <v>-2.823861333333333</v>
+        <v>-2.919124533333334</v>
       </c>
       <c r="O42">
-        <v>-0.7059653333333333</v>
+        <v>-0.7297811333333334</v>
       </c>
       <c r="P42">
-        <v>-2.117896</v>
+        <v>-2.1893434</v>
       </c>
       <c r="Q42">
-        <v>-0.137896</v>
+        <v>-0.2093434000000003</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1183287379562963</v>
+        <v>0.1195580385996234</v>
       </c>
       <c r="T42">
-        <v>1.12199650928113</v>
+        <v>1.141013399268946</v>
       </c>
       <c r="U42">
         <v>0.2358</v>
       </c>
       <c r="V42">
-        <v>0.0647329363979655</v>
+        <v>0.06315408429069805</v>
       </c>
       <c r="W42">
-        <v>0.2205359735973597</v>
+        <v>0.2209082669242534</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.2589317455918621</v>
+        <v>0.2526163371627922</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1611116322127217</v>
+        <v>0.1630116322127217</v>
       </c>
       <c r="C43">
-        <v>-2.080965766447251</v>
+        <v>-2.71657473333274</v>
       </c>
       <c r="D43">
-        <v>14.28803423355275</v>
+        <v>14.05642526666726</v>
       </c>
       <c r="E43">
-        <v>-7.335999999999999</v>
+        <v>-6.931999999999999</v>
       </c>
       <c r="F43">
-        <v>16.564</v>
+        <v>16.968</v>
       </c>
       <c r="G43">
         <v>0.195</v>
@@ -4807,37 +4807,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M43">
-        <v>3.9057912</v>
+        <v>4.0010544</v>
       </c>
       <c r="N43">
-        <v>-2.919124533333334</v>
+        <v>-3.014387733333333</v>
       </c>
       <c r="O43">
-        <v>-0.7297811333333334</v>
+        <v>-0.7535969333333333</v>
       </c>
       <c r="P43">
-        <v>-2.1893434</v>
+        <v>-2.2607908</v>
       </c>
       <c r="Q43">
-        <v>-0.2093434000000003</v>
+        <v>-0.2807908000000001</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1195580385996234</v>
+        <v>0.1208297289203065</v>
       </c>
       <c r="T43">
-        <v>1.141013399268946</v>
+        <v>1.160686044083927</v>
       </c>
       <c r="U43">
         <v>0.2358</v>
       </c>
       <c r="V43">
-        <v>0.06315408429069805</v>
+        <v>0.06165041561711</v>
       </c>
       <c r="W43">
-        <v>0.2209082669242534</v>
+        <v>0.2212628319974854</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.2526163371627922</v>
+        <v>0.2466016624684401</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1630116322127217</v>
+        <v>0.1649116322127217</v>
       </c>
       <c r="C44">
-        <v>-2.716574733332735</v>
+        <v>-3.344794715130751</v>
       </c>
       <c r="D44">
-        <v>14.05642526666727</v>
+        <v>13.83220528486925</v>
       </c>
       <c r="E44">
-        <v>-6.931999999999999</v>
+        <v>-6.527999999999999</v>
       </c>
       <c r="F44">
-        <v>16.968</v>
+        <v>17.372</v>
       </c>
       <c r="G44">
         <v>0.195</v>
@@ -4889,37 +4889,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M44">
-        <v>4.0010544</v>
+        <v>4.0963176</v>
       </c>
       <c r="N44">
-        <v>-3.014387733333333</v>
+        <v>-3.109650933333333</v>
       </c>
       <c r="O44">
-        <v>-0.7535969333333333</v>
+        <v>-0.7774127333333333</v>
       </c>
       <c r="P44">
-        <v>-2.2607908</v>
+        <v>-2.3322382</v>
       </c>
       <c r="Q44">
-        <v>-0.2807908000000001</v>
+        <v>-0.3522381999999999</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1208297289203065</v>
+        <v>0.1221460399539961</v>
       </c>
       <c r="T44">
-        <v>1.160686044083927</v>
+        <v>1.181048957138031</v>
       </c>
       <c r="U44">
         <v>0.2358</v>
       </c>
       <c r="V44">
-        <v>0.06165041561711</v>
+        <v>0.06021668502136326</v>
       </c>
       <c r="W44">
-        <v>0.2212628319974854</v>
+        <v>0.2216009056719626</v>
       </c>
       <c r="X44" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.2466016624684401</v>
+        <v>0.2408667400854531</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1649116322127217</v>
+        <v>0.1668116322127217</v>
       </c>
       <c r="C45">
-        <v>-3.344794715130751</v>
+        <v>-3.96597375453956</v>
       </c>
       <c r="D45">
-        <v>13.83220528486925</v>
+        <v>13.61502624546044</v>
       </c>
       <c r="E45">
-        <v>-6.527999999999999</v>
+        <v>-6.123999999999999</v>
       </c>
       <c r="F45">
-        <v>17.372</v>
+        <v>17.776</v>
       </c>
       <c r="G45">
         <v>0.195</v>
@@ -4971,37 +4971,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M45">
-        <v>4.0963176</v>
+        <v>4.191580800000001</v>
       </c>
       <c r="N45">
-        <v>-3.109650933333333</v>
+        <v>-3.204914133333334</v>
       </c>
       <c r="O45">
-        <v>-0.7774127333333333</v>
+        <v>-0.8012285333333334</v>
       </c>
       <c r="P45">
-        <v>-2.3322382</v>
+        <v>-2.4036856</v>
       </c>
       <c r="Q45">
-        <v>-0.3522381999999999</v>
+        <v>-0.4236856000000002</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1221460399539961</v>
+        <v>0.1235093620960317</v>
       </c>
       <c r="T45">
-        <v>1.181048957138031</v>
+        <v>1.202139117086925</v>
       </c>
       <c r="U45">
         <v>0.2358</v>
       </c>
       <c r="V45">
-        <v>0.06021668502136326</v>
+        <v>0.05884812399815045</v>
       </c>
       <c r="W45">
-        <v>0.2216009056719626</v>
+        <v>0.2219236123612361</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>0.2408667400854531</v>
+        <v>0.2353924959926018</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1668116322127217</v>
+        <v>0.1687116322127217</v>
       </c>
       <c r="C46">
-        <v>-3.96597375453956</v>
+        <v>-4.580438373719009</v>
       </c>
       <c r="D46">
-        <v>13.61502624546044</v>
+        <v>13.40456162628099</v>
       </c>
       <c r="E46">
-        <v>-6.123999999999999</v>
+        <v>-5.719999999999999</v>
       </c>
       <c r="F46">
-        <v>17.776</v>
+        <v>18.18</v>
       </c>
       <c r="G46">
         <v>0.195</v>
@@ -5053,37 +5053,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M46">
-        <v>4.191580800000001</v>
+        <v>4.286844</v>
       </c>
       <c r="N46">
-        <v>-3.204914133333334</v>
+        <v>-3.300177333333334</v>
       </c>
       <c r="O46">
-        <v>-0.8012285333333334</v>
+        <v>-0.8250443333333334</v>
       </c>
       <c r="P46">
-        <v>-2.4036856</v>
+        <v>-2.475133</v>
       </c>
       <c r="Q46">
-        <v>-0.4236856000000002</v>
+        <v>-0.495133</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1235093620960317</v>
+        <v>0.1249222595886869</v>
       </c>
       <c r="T46">
-        <v>1.202139117086925</v>
+        <v>1.22399619194305</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
       </c>
       <c r="V46">
-        <v>0.05884812399815045</v>
+        <v>0.05754038790930267</v>
       </c>
       <c r="W46">
-        <v>0.2219236123612361</v>
+        <v>0.2222319765309864</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.2353924959926018</v>
+        <v>0.2301615516372106</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1687116322127217</v>
+        <v>0.1706116322127217</v>
       </c>
       <c r="C47">
-        <v>-4.580438373719009</v>
+        <v>-5.188495212319811</v>
       </c>
       <c r="D47">
-        <v>13.40456162628099</v>
+        <v>13.20050478768019</v>
       </c>
       <c r="E47">
-        <v>-5.719999999999999</v>
+        <v>-5.315999999999999</v>
       </c>
       <c r="F47">
-        <v>18.18</v>
+        <v>18.584</v>
       </c>
       <c r="G47">
         <v>0.195</v>
@@ -5135,37 +5135,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M47">
-        <v>4.286844</v>
+        <v>4.3821072</v>
       </c>
       <c r="N47">
-        <v>-3.300177333333334</v>
+        <v>-3.395440533333333</v>
       </c>
       <c r="O47">
-        <v>-0.8250443333333334</v>
+        <v>-0.8488601333333333</v>
       </c>
       <c r="P47">
-        <v>-2.475133</v>
+        <v>-2.5465804</v>
       </c>
       <c r="Q47">
-        <v>-0.495133</v>
+        <v>-0.5665803999999999</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1249222595886869</v>
+        <v>0.126387486618107</v>
       </c>
       <c r="T47">
-        <v>1.22399619194305</v>
+        <v>1.246662788090144</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
       </c>
       <c r="V47">
-        <v>0.05754038790930267</v>
+        <v>0.05628950991127435</v>
       </c>
       <c r="W47">
-        <v>0.2222319765309864</v>
+        <v>0.2225269335629215</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.2301615516372106</v>
+        <v>0.2251580396450974</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1706116322127217</v>
+        <v>0.1725116322127217</v>
       </c>
       <c r="C48">
-        <v>-5.188495212319811</v>
+        <v>-5.790432518142588</v>
       </c>
       <c r="D48">
-        <v>13.20050478768019</v>
+        <v>13.00256748185741</v>
       </c>
       <c r="E48">
-        <v>-5.315999999999999</v>
+        <v>-4.911999999999999</v>
       </c>
       <c r="F48">
-        <v>18.584</v>
+        <v>18.988</v>
       </c>
       <c r="G48">
         <v>0.195</v>
@@ -5217,37 +5217,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M48">
-        <v>4.3821072</v>
+        <v>4.4773704</v>
       </c>
       <c r="N48">
-        <v>-3.395440533333333</v>
+        <v>-3.490703733333333</v>
       </c>
       <c r="O48">
-        <v>-0.8488601333333333</v>
+        <v>-0.8726759333333333</v>
       </c>
       <c r="P48">
-        <v>-2.5465804</v>
+        <v>-2.6180278</v>
       </c>
       <c r="Q48">
-        <v>-0.5665803999999999</v>
+        <v>-0.6380277999999997</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.126387486618107</v>
+        <v>0.127908005233543</v>
       </c>
       <c r="T48">
-        <v>1.246662788090144</v>
+        <v>1.270184727488071</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
       </c>
       <c r="V48">
-        <v>0.05628950991127435</v>
+        <v>0.05509186076422597</v>
       </c>
       <c r="W48">
-        <v>0.2225269335629215</v>
+        <v>0.2228093392317955</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.2251580396450974</v>
+        <v>0.2203674430569038</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1725116322127217</v>
+        <v>0.1744116322127217</v>
       </c>
       <c r="C49">
-        <v>-5.790432518142588</v>
+        <v>-6.386521505666419</v>
       </c>
       <c r="D49">
-        <v>13.00256748185741</v>
+        <v>12.81047849433358</v>
       </c>
       <c r="E49">
-        <v>-4.911999999999999</v>
+        <v>-4.507999999999999</v>
       </c>
       <c r="F49">
-        <v>18.988</v>
+        <v>19.392</v>
       </c>
       <c r="G49">
         <v>0.195</v>
@@ -5299,37 +5299,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M49">
-        <v>4.4773704</v>
+        <v>4.5726336</v>
       </c>
       <c r="N49">
-        <v>-3.490703733333333</v>
+        <v>-3.585966933333333</v>
       </c>
       <c r="O49">
-        <v>-0.8726759333333333</v>
+        <v>-0.8964917333333332</v>
       </c>
       <c r="P49">
-        <v>-2.6180278</v>
+        <v>-2.6894752</v>
       </c>
       <c r="Q49">
-        <v>-0.6380277999999997</v>
+        <v>-0.7094751999999995</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.127908005233543</v>
+        <v>0.1294870053341881</v>
       </c>
       <c r="T49">
-        <v>1.270184727488071</v>
+        <v>1.294611356862842</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
       </c>
       <c r="V49">
-        <v>0.05509186076422597</v>
+        <v>0.05394411366497126</v>
       </c>
       <c r="W49">
-        <v>0.2228093392317955</v>
+        <v>0.2230799779977998</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.2203674430569038</v>
+        <v>0.215776454659885</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1744116322127217</v>
+        <v>0.1763116322127217</v>
       </c>
       <c r="C50">
-        <v>-6.386521505666416</v>
+        <v>-6.977017595911935</v>
       </c>
       <c r="D50">
-        <v>12.81047849433358</v>
+        <v>12.62398240408806</v>
       </c>
       <c r="E50">
-        <v>-4.507999999999999</v>
+        <v>-4.103999999999999</v>
       </c>
       <c r="F50">
-        <v>19.392</v>
+        <v>19.796</v>
       </c>
       <c r="G50">
         <v>0.195</v>
@@ -5381,37 +5381,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M50">
-        <v>4.5726336</v>
+        <v>4.6678968</v>
       </c>
       <c r="N50">
-        <v>-3.585966933333333</v>
+        <v>-3.681230133333333</v>
       </c>
       <c r="O50">
-        <v>-0.8964917333333332</v>
+        <v>-0.9203075333333334</v>
       </c>
       <c r="P50">
-        <v>-2.6894752</v>
+        <v>-2.7609226</v>
       </c>
       <c r="Q50">
-        <v>-0.7094751999999995</v>
+        <v>-0.7809226000000002</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.129487005334188</v>
+        <v>0.1311279270074074</v>
       </c>
       <c r="T50">
-        <v>1.294611356862842</v>
+        <v>1.319995893271917</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
       </c>
       <c r="V50">
-        <v>0.05394411366497126</v>
+        <v>0.05284321338609429</v>
       </c>
       <c r="W50">
-        <v>0.2230799779977998</v>
+        <v>0.223339570283559</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.215776454659885</v>
+        <v>0.2113728535443772</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1763116322127217</v>
+        <v>0.1782116322127217</v>
       </c>
       <c r="C51">
-        <v>-6.977017595911935</v>
+        <v>-7.5621615495582</v>
       </c>
       <c r="D51">
-        <v>12.62398240408806</v>
+        <v>12.4428384504418</v>
       </c>
       <c r="E51">
-        <v>-4.103999999999999</v>
+        <v>-3.699999999999999</v>
       </c>
       <c r="F51">
-        <v>19.796</v>
+        <v>20.2</v>
       </c>
       <c r="G51">
         <v>0.195</v>
@@ -5463,37 +5463,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M51">
-        <v>4.6678968</v>
+        <v>4.76316</v>
       </c>
       <c r="N51">
-        <v>-3.681230133333333</v>
+        <v>-3.776493333333333</v>
       </c>
       <c r="O51">
-        <v>-0.9203075333333334</v>
+        <v>-0.9441233333333333</v>
       </c>
       <c r="P51">
-        <v>-2.7609226</v>
+        <v>-2.83237</v>
       </c>
       <c r="Q51">
-        <v>-0.7809226000000002</v>
+        <v>-0.8523700000000001</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1311279270074074</v>
+        <v>0.1328344855475556</v>
       </c>
       <c r="T51">
-        <v>1.319995893271917</v>
+        <v>1.346395811137356</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
       </c>
       <c r="V51">
-        <v>0.05284321338609429</v>
+        <v>0.0517863491183724</v>
       </c>
       <c r="W51">
-        <v>0.223339570283559</v>
+        <v>0.2235887788778878</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.2113728535443772</v>
+        <v>0.2071453964734896</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1782116322127217</v>
+        <v>0.1801116322127217</v>
       </c>
       <c r="C52">
-        <v>-7.5621615495582</v>
+        <v>-8.142180503883736</v>
       </c>
       <c r="D52">
-        <v>12.4428384504418</v>
+        <v>12.26681949611626</v>
       </c>
       <c r="E52">
-        <v>-3.699999999999999</v>
+        <v>-3.295999999999999</v>
       </c>
       <c r="F52">
-        <v>20.2</v>
+        <v>20.604</v>
       </c>
       <c r="G52">
         <v>0.195</v>
@@ -5545,37 +5545,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M52">
-        <v>4.76316</v>
+        <v>4.8584232</v>
       </c>
       <c r="N52">
-        <v>-3.776493333333333</v>
+        <v>-3.871756533333333</v>
       </c>
       <c r="O52">
-        <v>-0.9441233333333333</v>
+        <v>-0.9679391333333333</v>
       </c>
       <c r="P52">
-        <v>-2.83237</v>
+        <v>-2.9038174</v>
       </c>
       <c r="Q52">
-        <v>-0.8523700000000001</v>
+        <v>-0.9238173999999999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1328344855475556</v>
+        <v>0.134610699538322</v>
       </c>
       <c r="T52">
-        <v>1.346395811137356</v>
+        <v>1.373873276670771</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
       </c>
       <c r="V52">
-        <v>0.0517863491183724</v>
+        <v>0.05077093050820824</v>
       </c>
       <c r="W52">
-        <v>0.2235887788778878</v>
+        <v>0.2238282145861645</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.2071453964734896</v>
+        <v>0.203083722032833</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1801116322127217</v>
+        <v>0.1820116322127217</v>
       </c>
       <c r="C53">
-        <v>-8.142180503883736</v>
+        <v>-8.71728892292259</v>
       </c>
       <c r="D53">
-        <v>12.26681949611626</v>
+        <v>12.09571107707741</v>
       </c>
       <c r="E53">
-        <v>-3.295999999999999</v>
+        <v>-2.891999999999999</v>
       </c>
       <c r="F53">
-        <v>20.604</v>
+        <v>21.008</v>
       </c>
       <c r="G53">
         <v>0.195</v>
@@ -5627,37 +5627,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M53">
-        <v>4.8584232</v>
+        <v>4.9536864</v>
       </c>
       <c r="N53">
-        <v>-3.871756533333333</v>
+        <v>-3.967019733333333</v>
       </c>
       <c r="O53">
-        <v>-0.9679391333333333</v>
+        <v>-0.9917549333333332</v>
       </c>
       <c r="P53">
-        <v>-2.9038174</v>
+        <v>-2.9752648</v>
       </c>
       <c r="Q53">
-        <v>-0.9238173999999999</v>
+        <v>-0.9952647999999997</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.134610699538322</v>
+        <v>0.1364609224453704</v>
       </c>
       <c r="T53">
-        <v>1.373873276670771</v>
+        <v>1.402495636601412</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
       </c>
       <c r="V53">
-        <v>0.05077093050820824</v>
+        <v>0.04979456645997347</v>
       </c>
       <c r="W53">
-        <v>0.2238282145861645</v>
+        <v>0.2240584412287382</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.203083722032833</v>
+        <v>0.1991782658398938</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1820116322127217</v>
+        <v>0.1839116322127217</v>
       </c>
       <c r="C54">
-        <v>-8.71728892292259</v>
+        <v>-9.287689469192658</v>
       </c>
       <c r="D54">
-        <v>12.09571107707741</v>
+        <v>11.92931053080734</v>
       </c>
       <c r="E54">
-        <v>-2.891999999999999</v>
+        <v>-2.488</v>
       </c>
       <c r="F54">
-        <v>21.008</v>
+        <v>21.412</v>
       </c>
       <c r="G54">
         <v>0.195</v>
@@ -5709,37 +5709,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M54">
-        <v>4.9536864</v>
+        <v>5.0489496</v>
       </c>
       <c r="N54">
-        <v>-3.967019733333333</v>
+        <v>-4.062282933333334</v>
       </c>
       <c r="O54">
-        <v>-0.9917549333333332</v>
+        <v>-1.015570733333333</v>
       </c>
       <c r="P54">
-        <v>-2.9752648</v>
+        <v>-3.0467122</v>
       </c>
       <c r="Q54">
-        <v>-0.9952647999999997</v>
+        <v>-1.0667122</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1364609224453704</v>
+        <v>0.1383898782420804</v>
       </c>
       <c r="T54">
-        <v>1.402495636601412</v>
+        <v>1.432335969295059</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
       </c>
       <c r="V54">
-        <v>0.04979456645997347</v>
+        <v>0.04885504633808717</v>
       </c>
       <c r="W54">
-        <v>0.2240584412287382</v>
+        <v>0.2242799800734791</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.1991782658398938</v>
+        <v>0.1954201853523486</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1839116322127217</v>
+        <v>0.1858116322127217</v>
       </c>
       <c r="C55">
-        <v>-9.287689469192658</v>
+        <v>-9.853573804446295</v>
       </c>
       <c r="D55">
-        <v>11.92931053080734</v>
+        <v>11.7674261955537</v>
       </c>
       <c r="E55">
-        <v>-2.488</v>
+        <v>-2.084</v>
       </c>
       <c r="F55">
-        <v>21.412</v>
+        <v>21.816</v>
       </c>
       <c r="G55">
         <v>0.195</v>
@@ -5791,37 +5791,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M55">
-        <v>5.0489496</v>
+        <v>5.1442128</v>
       </c>
       <c r="N55">
-        <v>-4.062282933333334</v>
+        <v>-4.157546133333334</v>
       </c>
       <c r="O55">
-        <v>-1.015570733333333</v>
+        <v>-1.039386533333333</v>
       </c>
       <c r="P55">
-        <v>-3.0467122</v>
+        <v>-3.1181596</v>
       </c>
       <c r="Q55">
-        <v>-1.0667122</v>
+        <v>-1.1381596</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1383898782420804</v>
+        <v>0.1404027016821256</v>
       </c>
       <c r="T55">
-        <v>1.432335969295059</v>
+        <v>1.463473707757995</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
       </c>
       <c r="V55">
-        <v>0.04885504633808717</v>
+        <v>0.04795032325775223</v>
       </c>
       <c r="W55">
-        <v>0.2242799800734791</v>
+        <v>0.224493313775822</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.1954201853523486</v>
+        <v>0.1918012930310088</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1858116322127217</v>
+        <v>0.1877116322127217</v>
       </c>
       <c r="C56">
-        <v>-9.853573804446295</v>
+        <v>-10.41512332609536</v>
       </c>
       <c r="D56">
-        <v>11.7674261955537</v>
+        <v>11.60987667390464</v>
       </c>
       <c r="E56">
-        <v>-2.084</v>
+        <v>-1.679999999999996</v>
       </c>
       <c r="F56">
-        <v>21.816</v>
+        <v>22.22</v>
       </c>
       <c r="G56">
         <v>0.195</v>
@@ -5873,37 +5873,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M56">
-        <v>5.1442128</v>
+        <v>5.239476000000001</v>
       </c>
       <c r="N56">
-        <v>-4.157546133333334</v>
+        <v>-4.252809333333333</v>
       </c>
       <c r="O56">
-        <v>-1.039386533333333</v>
+        <v>-1.063202333333333</v>
       </c>
       <c r="P56">
-        <v>-3.1181596</v>
+        <v>-3.189607</v>
       </c>
       <c r="Q56">
-        <v>-1.1381596</v>
+        <v>-1.209607</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1404027016821256</v>
+        <v>0.1425049839417284</v>
       </c>
       <c r="T56">
-        <v>1.463473707757995</v>
+        <v>1.495995345708173</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
       </c>
       <c r="V56">
-        <v>0.04795032325775223</v>
+        <v>0.04707849919852036</v>
       </c>
       <c r="W56">
-        <v>0.224493313775822</v>
+        <v>0.2246988898889889</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.1918012930310088</v>
+        <v>0.1883139967940816</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1877116322127217</v>
+        <v>0.1896116322127217</v>
       </c>
       <c r="C57">
-        <v>-10.41512332609536</v>
+        <v>-10.97250984525948</v>
       </c>
       <c r="D57">
-        <v>11.60987667390464</v>
+        <v>11.45649015474052</v>
       </c>
       <c r="E57">
-        <v>-1.679999999999996</v>
+        <v>-1.275999999999996</v>
       </c>
       <c r="F57">
-        <v>22.22</v>
+        <v>22.624</v>
       </c>
       <c r="G57">
         <v>0.195</v>
@@ -5955,37 +5955,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M57">
-        <v>5.239476000000001</v>
+        <v>5.3347392</v>
       </c>
       <c r="N57">
-        <v>-4.252809333333333</v>
+        <v>-4.348072533333333</v>
       </c>
       <c r="O57">
-        <v>-1.063202333333333</v>
+        <v>-1.087018133333333</v>
       </c>
       <c r="P57">
-        <v>-3.189607</v>
+        <v>-3.2610544</v>
       </c>
       <c r="Q57">
-        <v>-1.209607</v>
+        <v>-1.2810544</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1425049839417284</v>
+        <v>0.1447028244858586</v>
       </c>
       <c r="T57">
-        <v>1.495995345708173</v>
+        <v>1.529995239928813</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
       </c>
       <c r="V57">
-        <v>0.04707849919852036</v>
+        <v>0.0462378117128325</v>
       </c>
       <c r="W57">
-        <v>0.2246988898889889</v>
+        <v>0.2248971239981141</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.1883139967940816</v>
+        <v>0.1849512468513301</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1896116322127217</v>
+        <v>0.1915116322127217</v>
       </c>
       <c r="C58">
-        <v>-10.97250984525948</v>
+        <v>-11.5258962117661</v>
       </c>
       <c r="D58">
-        <v>11.45649015474052</v>
+        <v>11.30710378823391</v>
       </c>
       <c r="E58">
-        <v>-1.275999999999996</v>
+        <v>-0.8719999999999963</v>
       </c>
       <c r="F58">
-        <v>22.624</v>
+        <v>23.028</v>
       </c>
       <c r="G58">
         <v>0.195</v>
@@ -6037,37 +6037,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M58">
-        <v>5.3347392</v>
+        <v>5.430002400000001</v>
       </c>
       <c r="N58">
-        <v>-4.348072533333333</v>
+        <v>-4.443335733333335</v>
       </c>
       <c r="O58">
-        <v>-1.087018133333333</v>
+        <v>-1.110833933333334</v>
       </c>
       <c r="P58">
-        <v>-3.2610544</v>
+        <v>-3.332501800000001</v>
       </c>
       <c r="Q58">
-        <v>-1.2810544</v>
+        <v>-1.352501800000001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1447028244858586</v>
+        <v>0.1470028901715763</v>
       </c>
       <c r="T58">
-        <v>1.529995239928813</v>
+        <v>1.565576524578321</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
       </c>
       <c r="V58">
-        <v>0.0462378117128325</v>
+        <v>0.04542662203365999</v>
       </c>
       <c r="W58">
-        <v>0.2248971239981141</v>
+        <v>0.225088402524463</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.1849512468513301</v>
+        <v>0.1817064881346399</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1915116322127217</v>
+        <v>0.1934116322127217</v>
       </c>
       <c r="C59">
-        <v>-11.5258962117661</v>
+        <v>-12.07543689088198</v>
       </c>
       <c r="D59">
-        <v>11.30710378823391</v>
+        <v>11.16156310911802</v>
       </c>
       <c r="E59">
-        <v>-0.8719999999999963</v>
+        <v>-0.4679999999999964</v>
       </c>
       <c r="F59">
-        <v>23.028</v>
+        <v>23.432</v>
       </c>
       <c r="G59">
         <v>0.195</v>
@@ -6119,37 +6119,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M59">
-        <v>5.430002400000001</v>
+        <v>5.525265600000001</v>
       </c>
       <c r="N59">
-        <v>-4.443335733333335</v>
+        <v>-4.538598933333335</v>
       </c>
       <c r="O59">
-        <v>-1.110833933333334</v>
+        <v>-1.134649733333334</v>
       </c>
       <c r="P59">
-        <v>-3.332501800000001</v>
+        <v>-3.403949200000001</v>
       </c>
       <c r="Q59">
-        <v>-1.352501800000001</v>
+        <v>-1.423949200000001</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1470028901715763</v>
+        <v>0.149412482794709</v>
       </c>
       <c r="T59">
-        <v>1.565576524578321</v>
+        <v>1.6028521561159</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
       </c>
       <c r="V59">
-        <v>0.04542662203365999</v>
+        <v>0.04464340441238999</v>
       </c>
       <c r="W59">
-        <v>0.225088402524463</v>
+        <v>0.2252730852395584</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.1817064881346399</v>
+        <v>0.1785736176495599</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1934116322127217</v>
+        <v>0.1953116322127217</v>
       </c>
       <c r="C60">
-        <v>-12.07543689088198</v>
+        <v>-12.62127849606994</v>
       </c>
       <c r="D60">
-        <v>11.16156310911802</v>
+        <v>11.01972150393006</v>
       </c>
       <c r="E60">
-        <v>-0.468</v>
+        <v>-0.06400000000000006</v>
       </c>
       <c r="F60">
-        <v>23.432</v>
+        <v>23.836</v>
       </c>
       <c r="G60">
         <v>0.195</v>
@@ -6201,37 +6201,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M60">
-        <v>5.5252656</v>
+        <v>5.6205288</v>
       </c>
       <c r="N60">
-        <v>-4.538598933333333</v>
+        <v>-4.633862133333333</v>
       </c>
       <c r="O60">
-        <v>-1.134649733333333</v>
+        <v>-1.158465533333333</v>
       </c>
       <c r="P60">
-        <v>-3.4039492</v>
+        <v>-3.475396599999999</v>
       </c>
       <c r="Q60">
-        <v>-1.4239492</v>
+        <v>-1.495396599999999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.149412482794709</v>
+        <v>0.1519396165214092</v>
       </c>
       <c r="T60">
-        <v>1.602852156115899</v>
+        <v>1.641946111143116</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
       </c>
       <c r="V60">
-        <v>0.04464340441239</v>
+        <v>0.04388673654099357</v>
       </c>
       <c r="W60">
-        <v>0.2252730852395584</v>
+        <v>0.2254515075236337</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.1785736176495601</v>
+        <v>0.1755469461639744</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1953116322127217</v>
+        <v>0.1972116322127217</v>
       </c>
       <c r="C61">
-        <v>-12.62127849606994</v>
+        <v>-13.16356028163349</v>
       </c>
       <c r="D61">
-        <v>11.01972150393006</v>
+        <v>10.88143971836651</v>
       </c>
       <c r="E61">
-        <v>-0.06400000000000006</v>
+        <v>0.3399999999999999</v>
       </c>
       <c r="F61">
-        <v>23.836</v>
+        <v>24.24</v>
       </c>
       <c r="G61">
         <v>0.195</v>
@@ -6283,37 +6283,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M61">
-        <v>5.6205288</v>
+        <v>5.715792</v>
       </c>
       <c r="N61">
-        <v>-4.633862133333333</v>
+        <v>-4.729125333333332</v>
       </c>
       <c r="O61">
-        <v>-1.158465533333333</v>
+        <v>-1.182281333333333</v>
       </c>
       <c r="P61">
-        <v>-3.475396599999999</v>
+        <v>-3.546843999999999</v>
       </c>
       <c r="Q61">
-        <v>-1.495396599999999</v>
+        <v>-1.566843999999999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1519396165214092</v>
+        <v>0.1545931069344444</v>
       </c>
       <c r="T61">
-        <v>1.641946111143116</v>
+        <v>1.682994763921694</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
       </c>
       <c r="V61">
-        <v>0.04388673654099357</v>
+        <v>0.04315529093197701</v>
       </c>
       <c r="W61">
-        <v>0.2254515075236337</v>
+        <v>0.2256239823982398</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.1755469461639744</v>
+        <v>0.1726211637279081</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.1972116322127217</v>
+        <v>0.1991116322127217</v>
       </c>
       <c r="C62">
-        <v>-13.16356028163349</v>
+        <v>-13.70241459872934</v>
       </c>
       <c r="D62">
-        <v>10.88143971836651</v>
+        <v>10.74658540127066</v>
       </c>
       <c r="E62">
-        <v>0.3399999999999999</v>
+        <v>0.7439999999999998</v>
       </c>
       <c r="F62">
-        <v>24.24</v>
+        <v>24.644</v>
       </c>
       <c r="G62">
         <v>0.195</v>
@@ -6365,37 +6365,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M62">
-        <v>5.715792</v>
+        <v>5.8110552</v>
       </c>
       <c r="N62">
-        <v>-4.729125333333332</v>
+        <v>-4.824388533333334</v>
       </c>
       <c r="O62">
-        <v>-1.182281333333333</v>
+        <v>-1.206097133333333</v>
       </c>
       <c r="P62">
-        <v>-3.546843999999999</v>
+        <v>-3.6182914</v>
       </c>
       <c r="Q62">
-        <v>-1.566843999999999</v>
+        <v>-1.6382914</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1545931069344444</v>
+        <v>0.1573826737789174</v>
       </c>
       <c r="T62">
-        <v>1.682994763921694</v>
+        <v>1.726148475817123</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
       </c>
       <c r="V62">
-        <v>0.04315529093197701</v>
+        <v>0.04244782714620689</v>
       </c>
       <c r="W62">
-        <v>0.2256239823982398</v>
+        <v>0.2257908023589244</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.1726211637279081</v>
+        <v>0.1697913085848275</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.1991116322127217</v>
+        <v>0.2010116322127217</v>
       </c>
       <c r="C63">
-        <v>-13.70241459872934</v>
+        <v>-14.23796731788656</v>
       </c>
       <c r="D63">
-        <v>10.74658540127066</v>
+        <v>10.61503268211344</v>
       </c>
       <c r="E63">
-        <v>0.7439999999999998</v>
+        <v>1.148</v>
       </c>
       <c r="F63">
-        <v>24.644</v>
+        <v>25.048</v>
       </c>
       <c r="G63">
         <v>0.195</v>
@@ -6447,37 +6447,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M63">
-        <v>5.8110552</v>
+        <v>5.9063184</v>
       </c>
       <c r="N63">
-        <v>-4.824388533333334</v>
+        <v>-4.919651733333334</v>
       </c>
       <c r="O63">
-        <v>-1.206097133333333</v>
+        <v>-1.229912933333333</v>
       </c>
       <c r="P63">
-        <v>-3.6182914</v>
+        <v>-3.6897388</v>
       </c>
       <c r="Q63">
-        <v>-1.6382914</v>
+        <v>-1.7097388</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1573826737789174</v>
+        <v>0.1603190599309942</v>
       </c>
       <c r="T63">
-        <v>1.726148475817123</v>
+        <v>1.771573435707047</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.04244782714620689</v>
+        <v>0.04176318477288097</v>
       </c>
       <c r="W63">
-        <v>0.2257908023589244</v>
+        <v>0.2259522410305547</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.1697913085848275</v>
+        <v>0.1670527390915238</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2010116322127217</v>
+        <v>0.2029116322127217</v>
       </c>
       <c r="C64">
-        <v>-14.23796731788656</v>
+        <v>-14.77033822086788</v>
       </c>
       <c r="D64">
-        <v>10.61503268211344</v>
+        <v>10.48666177913212</v>
       </c>
       <c r="E64">
-        <v>1.148</v>
+        <v>1.552</v>
       </c>
       <c r="F64">
-        <v>25.048</v>
+        <v>25.452</v>
       </c>
       <c r="G64">
         <v>0.195</v>
@@ -6529,37 +6529,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M64">
-        <v>5.9063184</v>
+        <v>6.0015816</v>
       </c>
       <c r="N64">
-        <v>-4.919651733333334</v>
+        <v>-5.014914933333333</v>
       </c>
       <c r="O64">
-        <v>-1.229912933333333</v>
+        <v>-1.253728733333333</v>
       </c>
       <c r="P64">
-        <v>-3.6897388</v>
+        <v>-3.7611862</v>
       </c>
       <c r="Q64">
-        <v>-1.7097388</v>
+        <v>-1.7811862</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1603190599309942</v>
+        <v>0.1634141696588589</v>
       </c>
       <c r="T64">
-        <v>1.771573435707047</v>
+        <v>1.819453798834264</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.04176318477288097</v>
+        <v>0.04110027707807334</v>
       </c>
       <c r="W64">
-        <v>0.2259522410305547</v>
+        <v>0.2261085546649903</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.1670527390915238</v>
+        <v>0.1644011083122933</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2029116322127217</v>
+        <v>0.2048116322127217</v>
       </c>
       <c r="C65">
-        <v>-14.77033822086788</v>
+        <v>-15.29964136443725</v>
       </c>
       <c r="D65">
-        <v>10.48666177913212</v>
+        <v>10.36135863556275</v>
       </c>
       <c r="E65">
-        <v>1.552</v>
+        <v>1.956</v>
       </c>
       <c r="F65">
-        <v>25.452</v>
+        <v>25.856</v>
       </c>
       <c r="G65">
         <v>0.195</v>
@@ -6611,37 +6611,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M65">
-        <v>6.0015816</v>
+        <v>6.0968448</v>
       </c>
       <c r="N65">
-        <v>-5.014914933333333</v>
+        <v>-5.110178133333333</v>
       </c>
       <c r="O65">
-        <v>-1.253728733333333</v>
+        <v>-1.277544533333333</v>
       </c>
       <c r="P65">
-        <v>-3.7611862</v>
+        <v>-3.8326336</v>
       </c>
       <c r="Q65">
-        <v>-1.7811862</v>
+        <v>-1.8526336</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1634141696588589</v>
+        <v>0.1666812299271605</v>
       </c>
       <c r="T65">
-        <v>1.819453798834264</v>
+        <v>1.869994182135216</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.04110027707807334</v>
+        <v>0.04045808524872845</v>
       </c>
       <c r="W65">
-        <v>0.2261085546649903</v>
+        <v>0.2262599834983499</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.1644011083122933</v>
+        <v>0.1618323409949137</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2048116322127217</v>
+        <v>0.2067116322127217</v>
       </c>
       <c r="C66">
-        <v>-15.29964136443725</v>
+        <v>-15.8259854183559</v>
       </c>
       <c r="D66">
-        <v>10.36135863556275</v>
+        <v>10.23901458164411</v>
       </c>
       <c r="E66">
-        <v>1.956</v>
+        <v>2.360000000000003</v>
       </c>
       <c r="F66">
-        <v>25.856</v>
+        <v>26.26</v>
       </c>
       <c r="G66">
         <v>0.195</v>
@@ -6693,37 +6693,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M66">
-        <v>6.0968448</v>
+        <v>6.192108000000001</v>
       </c>
       <c r="N66">
-        <v>-5.110178133333333</v>
+        <v>-5.205441333333335</v>
       </c>
       <c r="O66">
-        <v>-1.277544533333333</v>
+        <v>-1.301360333333334</v>
       </c>
       <c r="P66">
-        <v>-3.8326336</v>
+        <v>-3.904081000000001</v>
       </c>
       <c r="Q66">
-        <v>-1.8526336</v>
+        <v>-1.924081000000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1666812299271605</v>
+        <v>0.1701349793536508</v>
       </c>
       <c r="T66">
-        <v>1.869994182135216</v>
+        <v>1.92342258733908</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.04045808524872845</v>
+        <v>0.03983565316797877</v>
       </c>
       <c r="W66">
-        <v>0.2262599834983499</v>
+        <v>0.2264067529829906</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.1618323409949137</v>
+        <v>0.159342612671915</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2067116322127217</v>
+        <v>0.2086116322127217</v>
       </c>
       <c r="C67">
-        <v>-15.8259854183559</v>
+        <v>-16.34947397971192</v>
       </c>
       <c r="D67">
-        <v>10.23901458164411</v>
+        <v>10.11952602028809</v>
       </c>
       <c r="E67">
-        <v>2.360000000000003</v>
+        <v>2.764000000000003</v>
       </c>
       <c r="F67">
-        <v>26.26</v>
+        <v>26.664</v>
       </c>
       <c r="G67">
         <v>0.195</v>
@@ -6775,37 +6775,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M67">
-        <v>6.192108000000001</v>
+        <v>6.287371200000001</v>
       </c>
       <c r="N67">
-        <v>-5.205441333333335</v>
+        <v>-5.300704533333334</v>
       </c>
       <c r="O67">
-        <v>-1.301360333333334</v>
+        <v>-1.325176133333334</v>
       </c>
       <c r="P67">
-        <v>-3.904081000000001</v>
+        <v>-3.975528400000001</v>
       </c>
       <c r="Q67">
-        <v>-1.924081000000001</v>
+        <v>-1.995528400000001</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1701349793536508</v>
+        <v>0.1737918905111111</v>
       </c>
       <c r="T67">
-        <v>1.92342258733908</v>
+        <v>1.979993839907876</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.03983565316797877</v>
+        <v>0.03923208266543363</v>
       </c>
       <c r="W67">
-        <v>0.2264067529829906</v>
+        <v>0.2265490749074908</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.159342612671915</v>
+        <v>0.1569283306617345</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2086116322127217</v>
+        <v>0.2105116322127217</v>
       </c>
       <c r="C68">
-        <v>-16.34947397971192</v>
+        <v>-16.87020586549468</v>
       </c>
       <c r="D68">
-        <v>10.11952602028809</v>
+        <v>10.00279413450533</v>
       </c>
       <c r="E68">
-        <v>2.764000000000003</v>
+        <v>3.168000000000003</v>
       </c>
       <c r="F68">
-        <v>26.664</v>
+        <v>27.068</v>
       </c>
       <c r="G68">
         <v>0.195</v>
@@ -6857,37 +6857,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M68">
-        <v>6.287371200000001</v>
+        <v>6.382634400000001</v>
       </c>
       <c r="N68">
-        <v>-5.300704533333334</v>
+        <v>-5.395967733333334</v>
       </c>
       <c r="O68">
-        <v>-1.325176133333334</v>
+        <v>-1.348991933333334</v>
       </c>
       <c r="P68">
-        <v>-3.975528400000001</v>
+        <v>-4.0469758</v>
       </c>
       <c r="Q68">
-        <v>-1.995528400000001</v>
+        <v>-2.0669758</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1737918905111111</v>
+        <v>0.1776704326478115</v>
       </c>
       <c r="T68">
-        <v>1.979993839907876</v>
+        <v>2.039993653238418</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.03923208266543363</v>
+        <v>0.03864652919281522</v>
       </c>
       <c r="W68">
-        <v>0.2265490749074908</v>
+        <v>0.2266871484163342</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.1569283306617345</v>
+        <v>0.1545861167712608</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2105116322127217</v>
+        <v>0.2124116322127217</v>
       </c>
       <c r="C69">
-        <v>-16.87020586549468</v>
+        <v>-17.38827538515039</v>
       </c>
       <c r="D69">
-        <v>10.00279413450533</v>
+        <v>9.888724614849611</v>
       </c>
       <c r="E69">
-        <v>3.168000000000003</v>
+        <v>3.572000000000003</v>
       </c>
       <c r="F69">
-        <v>27.068</v>
+        <v>27.472</v>
       </c>
       <c r="G69">
         <v>0.195</v>
@@ -6939,37 +6939,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M69">
-        <v>6.382634400000001</v>
+        <v>6.4778976</v>
       </c>
       <c r="N69">
-        <v>-5.395967733333334</v>
+        <v>-5.491230933333334</v>
       </c>
       <c r="O69">
-        <v>-1.348991933333334</v>
+        <v>-1.372807733333334</v>
       </c>
       <c r="P69">
-        <v>-4.0469758</v>
+        <v>-4.118423200000001</v>
       </c>
       <c r="Q69">
-        <v>-2.0669758</v>
+        <v>-2.138423200000001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1776704326478115</v>
+        <v>0.1817913836680556</v>
       </c>
       <c r="T69">
-        <v>2.039993653238418</v>
+        <v>2.103743454902118</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.03864652919281522</v>
+        <v>0.03807819788115618</v>
       </c>
       <c r="W69">
-        <v>0.2266871484163342</v>
+        <v>0.2268211609396234</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.1545861167712608</v>
+        <v>0.1523127915246246</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2124116322127217</v>
+        <v>0.2143116322127217</v>
       </c>
       <c r="C70">
-        <v>-17.38827538515039</v>
+        <v>-17.90377259469908</v>
       </c>
       <c r="D70">
-        <v>9.888724614849611</v>
+        <v>9.777227405300916</v>
       </c>
       <c r="E70">
-        <v>3.572000000000003</v>
+        <v>3.976000000000003</v>
       </c>
       <c r="F70">
-        <v>27.472</v>
+        <v>27.876</v>
       </c>
       <c r="G70">
         <v>0.195</v>
@@ -7021,37 +7021,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M70">
-        <v>6.4778976</v>
+        <v>6.5731608</v>
       </c>
       <c r="N70">
-        <v>-5.491230933333334</v>
+        <v>-5.586494133333334</v>
       </c>
       <c r="O70">
-        <v>-1.372807733333334</v>
+        <v>-1.396623533333333</v>
       </c>
       <c r="P70">
-        <v>-4.118423200000001</v>
+        <v>-4.189870600000001</v>
       </c>
       <c r="Q70">
-        <v>-2.138423200000001</v>
+        <v>-2.209870600000001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1817913836680556</v>
+        <v>0.1861782024960574</v>
       </c>
       <c r="T70">
-        <v>2.103743454902118</v>
+        <v>2.171606146995735</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.03807819788115618</v>
+        <v>0.03752633994084957</v>
       </c>
       <c r="W70">
-        <v>0.2268211609396234</v>
+        <v>0.2269512890419477</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.1523127915246246</v>
+        <v>0.1501053597633982</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2143116322127217</v>
+        <v>0.2162116322127217</v>
       </c>
       <c r="C71">
-        <v>-17.90377259469908</v>
+        <v>-18.41678353385189</v>
       </c>
       <c r="D71">
-        <v>9.777227405300916</v>
+        <v>9.668216466148108</v>
       </c>
       <c r="E71">
-        <v>3.976000000000003</v>
+        <v>4.380000000000003</v>
       </c>
       <c r="F71">
-        <v>27.876</v>
+        <v>28.28</v>
       </c>
       <c r="G71">
         <v>0.195</v>
@@ -7103,37 +7103,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M71">
-        <v>6.5731608</v>
+        <v>6.668424000000001</v>
       </c>
       <c r="N71">
-        <v>-5.586494133333334</v>
+        <v>-5.681757333333334</v>
       </c>
       <c r="O71">
-        <v>-1.396623533333333</v>
+        <v>-1.420439333333333</v>
       </c>
       <c r="P71">
-        <v>-4.189870600000001</v>
+        <v>-4.261318</v>
       </c>
       <c r="Q71">
-        <v>-2.209870600000001</v>
+        <v>-2.281318</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1861782024960574</v>
+        <v>0.1908574759125926</v>
       </c>
       <c r="T71">
-        <v>2.171606146995735</v>
+        <v>2.24399301856226</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.03752633994084957</v>
+        <v>0.036990249370266</v>
       </c>
       <c r="W71">
-        <v>0.2269512890419477</v>
+        <v>0.2270776991984913</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.1501053597633982</v>
+        <v>0.1479609974810641</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2162116322127217</v>
+        <v>0.2181116322127217</v>
       </c>
       <c r="C72">
-        <v>-18.41678353385189</v>
+        <v>-18.92739044744089</v>
       </c>
       <c r="D72">
-        <v>9.668216466148108</v>
+        <v>9.56160955255911</v>
       </c>
       <c r="E72">
-        <v>4.380000000000003</v>
+        <v>4.784000000000002</v>
       </c>
       <c r="F72">
-        <v>28.28</v>
+        <v>28.684</v>
       </c>
       <c r="G72">
         <v>0.195</v>
@@ -7185,37 +7185,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M72">
-        <v>6.668424000000001</v>
+        <v>6.763687200000001</v>
       </c>
       <c r="N72">
-        <v>-5.681757333333334</v>
+        <v>-5.777020533333333</v>
       </c>
       <c r="O72">
-        <v>-1.420439333333333</v>
+        <v>-1.444255133333333</v>
       </c>
       <c r="P72">
-        <v>-4.261318</v>
+        <v>-4.3327654</v>
       </c>
       <c r="Q72">
-        <v>-2.281318</v>
+        <v>-2.3527654</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1908574759125926</v>
+        <v>0.1958594578406131</v>
       </c>
       <c r="T72">
-        <v>2.24399301856226</v>
+        <v>2.321372088167855</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.036990249370266</v>
+        <v>0.03646925994251578</v>
       </c>
       <c r="W72">
-        <v>0.2270776991984913</v>
+        <v>0.2272005485055548</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.1479609974810641</v>
+        <v>0.1458770397700632</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2181116322127217</v>
+        <v>0.2200116322127217</v>
       </c>
       <c r="C73">
-        <v>-18.92739044744089</v>
+        <v>-19.43567199235908</v>
       </c>
       <c r="D73">
-        <v>9.56160955255911</v>
+        <v>9.457328007640921</v>
       </c>
       <c r="E73">
-        <v>4.783999999999999</v>
+        <v>5.187999999999999</v>
       </c>
       <c r="F73">
-        <v>28.684</v>
+        <v>29.088</v>
       </c>
       <c r="G73">
         <v>0.195</v>
@@ -7267,37 +7267,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M73">
-        <v>6.7636872</v>
+        <v>6.858950399999999</v>
       </c>
       <c r="N73">
-        <v>-5.777020533333333</v>
+        <v>-5.872283733333333</v>
       </c>
       <c r="O73">
-        <v>-1.444255133333333</v>
+        <v>-1.468070933333333</v>
       </c>
       <c r="P73">
-        <v>-4.3327654</v>
+        <v>-4.4042128</v>
       </c>
       <c r="Q73">
-        <v>-2.3527654</v>
+        <v>-2.4242128</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.195859457840613</v>
+        <v>0.2012187241920635</v>
       </c>
       <c r="T73">
-        <v>2.321372088167854</v>
+        <v>2.404278234173849</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.03646925994251578</v>
+        <v>0.03596274244331417</v>
       </c>
       <c r="W73">
-        <v>0.2272005485055548</v>
+        <v>0.2273199853318665</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.1458770397700631</v>
+        <v>0.1438509697732566</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2200116322127217</v>
+        <v>0.2219116322127216</v>
       </c>
       <c r="C74">
-        <v>-19.43567199235908</v>
+        <v>-19.94170343110478</v>
       </c>
       <c r="D74">
-        <v>9.457328007640921</v>
+        <v>9.355296568895218</v>
       </c>
       <c r="E74">
-        <v>5.187999999999999</v>
+        <v>5.591999999999999</v>
       </c>
       <c r="F74">
-        <v>29.088</v>
+        <v>29.492</v>
       </c>
       <c r="G74">
         <v>0.195</v>
@@ -7349,37 +7349,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M74">
-        <v>6.858950399999999</v>
+        <v>6.954213599999999</v>
       </c>
       <c r="N74">
-        <v>-5.872283733333333</v>
+        <v>-5.967546933333333</v>
       </c>
       <c r="O74">
-        <v>-1.468070933333333</v>
+        <v>-1.491886733333333</v>
       </c>
       <c r="P74">
-        <v>-4.4042128</v>
+        <v>-4.4756602</v>
       </c>
       <c r="Q74">
-        <v>-2.4242128</v>
+        <v>-2.4956602</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2012187241920635</v>
+        <v>0.206974973236214</v>
       </c>
       <c r="T74">
-        <v>2.404278234173849</v>
+        <v>2.493325576180287</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.03596274244331417</v>
+        <v>0.03547010213587151</v>
       </c>
       <c r="W74">
-        <v>0.2273199853318665</v>
+        <v>0.2274361499163615</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.1438509697732566</v>
+        <v>0.1418804085434859</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2219116322127216</v>
+        <v>0.2238116322127217</v>
       </c>
       <c r="C75">
-        <v>-19.94170343110478</v>
+        <v>-20.44555681293131</v>
       </c>
       <c r="D75">
-        <v>9.355296568895218</v>
+        <v>9.255443187068687</v>
       </c>
       <c r="E75">
-        <v>5.591999999999999</v>
+        <v>5.995999999999999</v>
       </c>
       <c r="F75">
-        <v>29.492</v>
+        <v>29.896</v>
       </c>
       <c r="G75">
         <v>0.195</v>
@@ -7431,37 +7431,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M75">
-        <v>6.954213599999999</v>
+        <v>7.0494768</v>
       </c>
       <c r="N75">
-        <v>-5.967546933333333</v>
+        <v>-6.062810133333333</v>
       </c>
       <c r="O75">
-        <v>-1.491886733333333</v>
+        <v>-1.515702533333333</v>
       </c>
       <c r="P75">
-        <v>-4.4756602</v>
+        <v>-4.547107599999999</v>
       </c>
       <c r="Q75">
-        <v>-2.4956602</v>
+        <v>-2.567107599999999</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.206974973236214</v>
+        <v>0.213174010668376</v>
       </c>
       <c r="T75">
-        <v>2.493325576180287</v>
+        <v>2.589222713725683</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.03547010213587151</v>
+        <v>0.03499077643133271</v>
       </c>
       <c r="W75">
-        <v>0.2274361499163615</v>
+        <v>0.2275491749174917</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.1418804085434859</v>
+        <v>0.1399631057253309</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2238116322127217</v>
+        <v>0.2257116322127217</v>
       </c>
       <c r="C76">
-        <v>-20.44555681293131</v>
+        <v>-20.94730114351822</v>
       </c>
       <c r="D76">
-        <v>9.255443187068687</v>
+        <v>9.157698856481778</v>
       </c>
       <c r="E76">
-        <v>5.995999999999999</v>
+        <v>6.399999999999999</v>
       </c>
       <c r="F76">
-        <v>29.896</v>
+        <v>30.3</v>
       </c>
       <c r="G76">
         <v>0.195</v>
@@ -7513,37 +7513,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M76">
-        <v>7.0494768</v>
+        <v>7.14474</v>
       </c>
       <c r="N76">
-        <v>-6.062810133333333</v>
+        <v>-6.158073333333332</v>
       </c>
       <c r="O76">
-        <v>-1.515702533333333</v>
+        <v>-1.539518333333333</v>
       </c>
       <c r="P76">
-        <v>-4.547107599999999</v>
+        <v>-4.618554999999999</v>
       </c>
       <c r="Q76">
-        <v>-2.567107599999999</v>
+        <v>-2.638554999999999</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.213174010668376</v>
+        <v>0.2198689710951111</v>
       </c>
       <c r="T76">
-        <v>2.589222713725683</v>
+        <v>2.692791622274711</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.03499077643133271</v>
+        <v>0.03452423274558161</v>
       </c>
       <c r="W76">
-        <v>0.2275491749174917</v>
+        <v>0.2276591859185919</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.1399631057253309</v>
+        <v>0.1380969309823264</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2257116322127217</v>
+        <v>0.2276116322127217</v>
       </c>
       <c r="C77">
-        <v>-20.94730114351822</v>
+        <v>-21.44700254400374</v>
       </c>
       <c r="D77">
-        <v>9.157698856481778</v>
+        <v>9.061997455996259</v>
       </c>
       <c r="E77">
-        <v>6.399999999999999</v>
+        <v>6.804000000000002</v>
       </c>
       <c r="F77">
-        <v>30.3</v>
+        <v>30.704</v>
       </c>
       <c r="G77">
         <v>0.195</v>
@@ -7595,37 +7595,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M77">
-        <v>7.14474</v>
+        <v>7.2400032</v>
       </c>
       <c r="N77">
-        <v>-6.158073333333332</v>
+        <v>-6.253336533333334</v>
       </c>
       <c r="O77">
-        <v>-1.539518333333333</v>
+        <v>-1.563334133333333</v>
       </c>
       <c r="P77">
-        <v>-4.618554999999999</v>
+        <v>-4.690002400000001</v>
       </c>
       <c r="Q77">
-        <v>-2.638554999999999</v>
+        <v>-2.710002400000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2198689710951111</v>
+        <v>0.2271218448907407</v>
       </c>
       <c r="T77">
-        <v>2.692791622274711</v>
+        <v>2.804991273202824</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.03452423274558161</v>
+        <v>0.034069966525245</v>
       </c>
       <c r="W77">
-        <v>0.2276591859185919</v>
+        <v>0.2277663018933472</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.1380969309823264</v>
+        <v>0.13627986610098</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2276116322127217</v>
+        <v>0.2295116322127217</v>
       </c>
       <c r="C78">
-        <v>-21.44700254400374</v>
+        <v>-21.94472440014868</v>
       </c>
       <c r="D78">
-        <v>9.061997455996259</v>
+        <v>8.968275599851317</v>
       </c>
       <c r="E78">
-        <v>6.804000000000002</v>
+        <v>7.208000000000002</v>
       </c>
       <c r="F78">
-        <v>30.704</v>
+        <v>31.108</v>
       </c>
       <c r="G78">
         <v>0.195</v>
@@ -7677,37 +7677,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M78">
-        <v>7.2400032</v>
+        <v>7.3352664</v>
       </c>
       <c r="N78">
-        <v>-6.253336533333334</v>
+        <v>-6.348599733333334</v>
       </c>
       <c r="O78">
-        <v>-1.563334133333333</v>
+        <v>-1.587149933333333</v>
       </c>
       <c r="P78">
-        <v>-4.690002400000001</v>
+        <v>-4.7614498</v>
       </c>
       <c r="Q78">
-        <v>-2.710002400000001</v>
+        <v>-2.7814498</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2271218448907407</v>
+        <v>0.2350054033642512</v>
       </c>
       <c r="T78">
-        <v>2.804991273202824</v>
+        <v>2.926947415515991</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.034069966525245</v>
+        <v>0.03362749942751455</v>
       </c>
       <c r="W78">
-        <v>0.2277663018933472</v>
+        <v>0.2278706356349921</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.13627986610098</v>
+        <v>0.1345099977100581</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2295116322127217</v>
+        <v>0.2314116322127217</v>
       </c>
       <c r="C79">
-        <v>-21.94472440014868</v>
+        <v>-22.4405275023389</v>
       </c>
       <c r="D79">
-        <v>8.968275599851317</v>
+        <v>8.876472497661101</v>
       </c>
       <c r="E79">
-        <v>7.208000000000002</v>
+        <v>7.612000000000002</v>
       </c>
       <c r="F79">
-        <v>31.108</v>
+        <v>31.512</v>
       </c>
       <c r="G79">
         <v>0.195</v>
@@ -7759,37 +7759,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M79">
-        <v>7.3352664</v>
+        <v>7.430529600000001</v>
       </c>
       <c r="N79">
-        <v>-6.348599733333334</v>
+        <v>-6.443862933333333</v>
       </c>
       <c r="O79">
-        <v>-1.587149933333333</v>
+        <v>-1.610965733333333</v>
       </c>
       <c r="P79">
-        <v>-4.7614498</v>
+        <v>-4.8328972</v>
       </c>
       <c r="Q79">
-        <v>-2.7814498</v>
+        <v>-2.8528972</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2350054033642512</v>
+        <v>0.2436056489717172</v>
       </c>
       <c r="T79">
-        <v>2.926947415515991</v>
+        <v>3.059990479857627</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.03362749942751455</v>
+        <v>0.03319637763998231</v>
       </c>
       <c r="W79">
-        <v>0.2278706356349921</v>
+        <v>0.2279722941524922</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.1345099977100581</v>
+        <v>0.1327855105599293</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2314116322127217</v>
+        <v>0.2333116322127217</v>
       </c>
       <c r="C80">
-        <v>-22.4405275023389</v>
+        <v>-22.93447017707613</v>
       </c>
       <c r="D80">
-        <v>8.876472497661101</v>
+        <v>8.786529822923869</v>
       </c>
       <c r="E80">
-        <v>7.612000000000002</v>
+        <v>8.016000000000002</v>
       </c>
       <c r="F80">
-        <v>31.512</v>
+        <v>31.916</v>
       </c>
       <c r="G80">
         <v>0.195</v>
@@ -7841,37 +7841,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M80">
-        <v>7.430529600000001</v>
+        <v>7.525792800000001</v>
       </c>
       <c r="N80">
-        <v>-6.443862933333333</v>
+        <v>-6.539126133333333</v>
       </c>
       <c r="O80">
-        <v>-1.610965733333333</v>
+        <v>-1.634781533333333</v>
       </c>
       <c r="P80">
-        <v>-4.8328972</v>
+        <v>-4.9043446</v>
       </c>
       <c r="Q80">
-        <v>-2.8528972</v>
+        <v>-2.9243446</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2436056489717172</v>
+        <v>0.2530249655894181</v>
       </c>
       <c r="T80">
-        <v>3.059990479857627</v>
+        <v>3.2057043122318</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.03319637763998231</v>
+        <v>0.0327761703280838</v>
       </c>
       <c r="W80">
-        <v>0.2279722941524922</v>
+        <v>0.2280713790366379</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.1327855105599293</v>
+        <v>0.1311046813123352</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2333116322127217</v>
+        <v>0.2352116322127217</v>
       </c>
       <c r="C81">
-        <v>-22.93447017707613</v>
+        <v>-23.42660841055488</v>
       </c>
       <c r="D81">
-        <v>8.786529822923869</v>
+        <v>8.698391589445125</v>
       </c>
       <c r="E81">
-        <v>8.016000000000002</v>
+        <v>8.420000000000002</v>
       </c>
       <c r="F81">
-        <v>31.916</v>
+        <v>32.32</v>
       </c>
       <c r="G81">
         <v>0.195</v>
@@ -7923,37 +7923,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M81">
-        <v>7.525792800000001</v>
+        <v>7.621056</v>
       </c>
       <c r="N81">
-        <v>-6.539126133333333</v>
+        <v>-6.634389333333333</v>
       </c>
       <c r="O81">
-        <v>-1.634781533333333</v>
+        <v>-1.658597333333333</v>
       </c>
       <c r="P81">
-        <v>-4.9043446</v>
+        <v>-4.975792</v>
       </c>
       <c r="Q81">
-        <v>-2.9243446</v>
+        <v>-2.995792</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2530249655894181</v>
+        <v>0.2633862138688889</v>
       </c>
       <c r="T81">
-        <v>3.2057043122318</v>
+        <v>3.36598952784339</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.0327761703280838</v>
+        <v>0.03236646819898275</v>
       </c>
       <c r="W81">
-        <v>0.2280713790366379</v>
+        <v>0.2281679867986799</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.1311046813123352</v>
+        <v>0.129465872795931</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2352116322127217</v>
+        <v>0.2371116322127217</v>
       </c>
       <c r="C82">
-        <v>-23.42660841055488</v>
+        <v>-23.91699596487551</v>
       </c>
       <c r="D82">
-        <v>8.698391589445125</v>
+        <v>8.612004035124491</v>
       </c>
       <c r="E82">
-        <v>8.420000000000002</v>
+        <v>8.824000000000005</v>
       </c>
       <c r="F82">
-        <v>32.32</v>
+        <v>32.724</v>
       </c>
       <c r="G82">
         <v>0.195</v>
@@ -8005,37 +8005,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M82">
-        <v>7.621056</v>
+        <v>7.716319200000001</v>
       </c>
       <c r="N82">
-        <v>-6.634389333333333</v>
+        <v>-6.729652533333335</v>
       </c>
       <c r="O82">
-        <v>-1.658597333333333</v>
+        <v>-1.682413133333334</v>
       </c>
       <c r="P82">
-        <v>-4.975792</v>
+        <v>-5.0472394</v>
       </c>
       <c r="Q82">
-        <v>-2.995792</v>
+        <v>-3.067239400000001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2633862138688889</v>
+        <v>0.2748381198619884</v>
       </c>
       <c r="T82">
-        <v>3.36598952784339</v>
+        <v>3.543146871414094</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.03236646819898275</v>
+        <v>0.03196688217183481</v>
       </c>
       <c r="W82">
-        <v>0.2281679867986799</v>
+        <v>0.2282622091838813</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.129465872795931</v>
+        <v>0.1278675286873392</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2371116322127217</v>
+        <v>0.2390116322127217</v>
       </c>
       <c r="C83">
-        <v>-23.91699596487551</v>
+        <v>-24.4056844874005</v>
       </c>
       <c r="D83">
-        <v>8.612004035124491</v>
+        <v>8.5273155125995</v>
       </c>
       <c r="E83">
-        <v>8.824000000000005</v>
+        <v>9.228000000000002</v>
       </c>
       <c r="F83">
-        <v>32.724</v>
+        <v>33.128</v>
       </c>
       <c r="G83">
         <v>0.195</v>
@@ -8087,37 +8087,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M83">
-        <v>7.716319200000001</v>
+        <v>7.811582400000001</v>
       </c>
       <c r="N83">
-        <v>-6.729652533333335</v>
+        <v>-6.824915733333334</v>
       </c>
       <c r="O83">
-        <v>-1.682413133333334</v>
+        <v>-1.706228933333334</v>
       </c>
       <c r="P83">
-        <v>-5.0472394</v>
+        <v>-5.118686800000001</v>
       </c>
       <c r="Q83">
-        <v>-3.067239400000001</v>
+        <v>-3.138686800000001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2748381198619884</v>
+        <v>0.2875624598543211</v>
       </c>
       <c r="T83">
-        <v>3.543146871414094</v>
+        <v>3.739988364270433</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.03196688217183481</v>
+        <v>0.03157704214534902</v>
       </c>
       <c r="W83">
-        <v>0.2282622091838813</v>
+        <v>0.2283541334621267</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.1278675286873392</v>
+        <v>0.126308168581396</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2390116322127217</v>
+        <v>0.2409116322127217</v>
       </c>
       <c r="C84">
-        <v>-24.4056844874005</v>
+        <v>-24.89272361372115</v>
       </c>
       <c r="D84">
-        <v>8.5273155125995</v>
+        <v>8.444276386278858</v>
       </c>
       <c r="E84">
-        <v>9.228000000000002</v>
+        <v>9.632000000000005</v>
       </c>
       <c r="F84">
-        <v>33.128</v>
+        <v>33.532</v>
       </c>
       <c r="G84">
         <v>0.195</v>
@@ -8169,37 +8169,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M84">
-        <v>7.811582400000001</v>
+        <v>7.906845600000001</v>
       </c>
       <c r="N84">
-        <v>-6.824915733333334</v>
+        <v>-6.920178933333334</v>
       </c>
       <c r="O84">
-        <v>-1.706228933333334</v>
+        <v>-1.730044733333334</v>
       </c>
       <c r="P84">
-        <v>-5.118686800000001</v>
+        <v>-5.190134200000001</v>
       </c>
       <c r="Q84">
-        <v>-3.138686800000001</v>
+        <v>-3.210134200000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2875624598543211</v>
+        <v>0.3017837810222223</v>
       </c>
       <c r="T84">
-        <v>3.739988364270433</v>
+        <v>3.959987679815753</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.03157704214534902</v>
+        <v>0.0311965958544412</v>
       </c>
       <c r="W84">
-        <v>0.2283541334621267</v>
+        <v>0.2284438426975228</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.126308168581396</v>
+        <v>0.1247863834177648</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2409116322127217</v>
+        <v>0.2428116322127217</v>
       </c>
       <c r="C85">
-        <v>-24.89272361372115</v>
+        <v>-25.3781610646662</v>
       </c>
       <c r="D85">
-        <v>8.444276386278858</v>
+        <v>8.362838935333796</v>
       </c>
       <c r="E85">
-        <v>9.632000000000005</v>
+        <v>10.036</v>
       </c>
       <c r="F85">
-        <v>33.532</v>
+        <v>33.936</v>
       </c>
       <c r="G85">
         <v>0.195</v>
@@ -8251,37 +8251,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M85">
-        <v>7.906845600000001</v>
+        <v>8.0021088</v>
       </c>
       <c r="N85">
-        <v>-6.920178933333334</v>
+        <v>-7.015442133333334</v>
       </c>
       <c r="O85">
-        <v>-1.730044733333334</v>
+        <v>-1.753860533333333</v>
       </c>
       <c r="P85">
-        <v>-5.190134200000001</v>
+        <v>-5.2615816</v>
       </c>
       <c r="Q85">
-        <v>-3.210134200000001</v>
+        <v>-3.2815816</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3017837810222223</v>
+        <v>0.3177827673361113</v>
       </c>
       <c r="T85">
-        <v>3.959987679815753</v>
+        <v>4.207486909804238</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.0311965958544412</v>
+        <v>0.030825207808555</v>
       </c>
       <c r="W85">
-        <v>0.2284438426975228</v>
+        <v>0.2285314159987427</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.1247863834177648</v>
+        <v>0.12330083123422</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2428116322127217</v>
+        <v>0.2447116322127217</v>
       </c>
       <c r="C86">
-        <v>-25.3781610646662</v>
+        <v>-25.86204273775076</v>
       </c>
       <c r="D86">
-        <v>8.362838935333802</v>
+        <v>8.282957262249234</v>
       </c>
       <c r="E86">
-        <v>10.036</v>
+        <v>10.44</v>
       </c>
       <c r="F86">
-        <v>33.936</v>
+        <v>34.34</v>
       </c>
       <c r="G86">
         <v>0.195</v>
@@ -8333,37 +8333,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M86">
-        <v>8.0021088</v>
+        <v>8.097372</v>
       </c>
       <c r="N86">
-        <v>-7.015442133333334</v>
+        <v>-7.110705333333334</v>
       </c>
       <c r="O86">
-        <v>-1.753860533333333</v>
+        <v>-1.777676333333333</v>
       </c>
       <c r="P86">
-        <v>-5.2615816</v>
+        <v>-5.333029</v>
       </c>
       <c r="Q86">
-        <v>-3.2815816</v>
+        <v>-3.353029</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3177827673361111</v>
+        <v>0.3359149518251852</v>
       </c>
       <c r="T86">
-        <v>4.207486909804236</v>
+        <v>4.487986037124518</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.030825207808555</v>
+        <v>0.03046255830492494</v>
       </c>
       <c r="W86">
-        <v>0.2285314159987427</v>
+        <v>0.2286169287516987</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.12330083123422</v>
+        <v>0.1218502332196997</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2447116322127217</v>
+        <v>0.2466116322127217</v>
       </c>
       <c r="C87">
-        <v>-25.86204273775076</v>
+        <v>-26.34441279343361</v>
       </c>
       <c r="D87">
-        <v>8.282957262249234</v>
+        <v>8.204587206566391</v>
       </c>
       <c r="E87">
-        <v>10.44</v>
+        <v>10.844</v>
       </c>
       <c r="F87">
-        <v>34.34</v>
+        <v>34.744</v>
       </c>
       <c r="G87">
         <v>0.195</v>
@@ -8415,37 +8415,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M87">
-        <v>8.097372</v>
+        <v>8.1926352</v>
       </c>
       <c r="N87">
-        <v>-7.110705333333334</v>
+        <v>-7.205968533333333</v>
       </c>
       <c r="O87">
-        <v>-1.777676333333333</v>
+        <v>-1.801492133333333</v>
       </c>
       <c r="P87">
-        <v>-5.333029</v>
+        <v>-5.4044764</v>
       </c>
       <c r="Q87">
-        <v>-3.353029</v>
+        <v>-3.4244764</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3359149518251852</v>
+        <v>0.356637448384127</v>
       </c>
       <c r="T87">
-        <v>4.487986037124518</v>
+        <v>4.808556468347698</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.03046255830492494</v>
+        <v>0.03010834251068163</v>
       </c>
       <c r="W87">
-        <v>0.2286169287516987</v>
+        <v>0.2287004528359813</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.1218502332196997</v>
+        <v>0.1204333700427265</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2466116322127217</v>
+        <v>0.2485116322127217</v>
       </c>
       <c r="C88">
-        <v>-26.34441279343361</v>
+        <v>-26.82531373652363</v>
       </c>
       <c r="D88">
-        <v>8.204587206566391</v>
+        <v>8.127686263476367</v>
       </c>
       <c r="E88">
-        <v>10.844</v>
+        <v>11.248</v>
       </c>
       <c r="F88">
-        <v>34.744</v>
+        <v>35.148</v>
       </c>
       <c r="G88">
         <v>0.195</v>
@@ -8497,37 +8497,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M88">
-        <v>8.1926352</v>
+        <v>8.2878984</v>
       </c>
       <c r="N88">
-        <v>-7.205968533333333</v>
+        <v>-7.301231733333333</v>
       </c>
       <c r="O88">
-        <v>-1.801492133333333</v>
+        <v>-1.825307933333333</v>
       </c>
       <c r="P88">
-        <v>-5.4044764</v>
+        <v>-5.4759238</v>
       </c>
       <c r="Q88">
-        <v>-3.4244764</v>
+        <v>-3.4959238</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.356637448384127</v>
+        <v>0.3805480213367521</v>
       </c>
       <c r="T88">
-        <v>4.808556468347698</v>
+        <v>5.178445427451367</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.03010834251068163</v>
+        <v>0.02976226960826</v>
       </c>
       <c r="W88">
-        <v>0.2287004528359813</v>
+        <v>0.2287820568263723</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.1204333700427265</v>
+        <v>0.1190490784330399</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2485116322127217</v>
+        <v>0.2504116322127217</v>
       </c>
       <c r="C89">
-        <v>-26.82531373652363</v>
+        <v>-27.30478649305074</v>
       </c>
       <c r="D89">
-        <v>8.127686263476367</v>
+        <v>8.05221350694926</v>
       </c>
       <c r="E89">
-        <v>11.248</v>
+        <v>11.652</v>
       </c>
       <c r="F89">
-        <v>35.148</v>
+        <v>35.552</v>
       </c>
       <c r="G89">
         <v>0.195</v>
@@ -8579,37 +8579,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M89">
-        <v>8.2878984</v>
+        <v>8.383161600000001</v>
       </c>
       <c r="N89">
-        <v>-7.301231733333333</v>
+        <v>-7.396494933333335</v>
       </c>
       <c r="O89">
-        <v>-1.825307933333333</v>
+        <v>-1.849123733333334</v>
       </c>
       <c r="P89">
-        <v>-5.4759238</v>
+        <v>-5.547371200000001</v>
       </c>
       <c r="Q89">
-        <v>-3.4959238</v>
+        <v>-3.567371200000001</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3805480213367521</v>
+        <v>0.4084436897814815</v>
       </c>
       <c r="T89">
-        <v>5.178445427451367</v>
+        <v>5.609982546405648</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.02976226960826</v>
+        <v>0.02942406199907523</v>
       </c>
       <c r="W89">
-        <v>0.2287820568263723</v>
+        <v>0.2288618061806181</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.1190490784330399</v>
+        <v>0.1176962479963009</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2504116322127217</v>
+        <v>0.2523116322127217</v>
       </c>
       <c r="C90">
-        <v>-27.30478649305074</v>
+        <v>-27.78287048289323</v>
       </c>
       <c r="D90">
-        <v>8.05221350694926</v>
+        <v>7.978129517106767</v>
       </c>
       <c r="E90">
-        <v>11.652</v>
+        <v>12.056</v>
       </c>
       <c r="F90">
-        <v>35.552</v>
+        <v>35.956</v>
       </c>
       <c r="G90">
         <v>0.195</v>
@@ -8661,37 +8661,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M90">
-        <v>8.383161600000001</v>
+        <v>8.478424799999999</v>
       </c>
       <c r="N90">
-        <v>-7.396494933333335</v>
+        <v>-7.491758133333333</v>
       </c>
       <c r="O90">
-        <v>-1.849123733333334</v>
+        <v>-1.872939533333333</v>
       </c>
       <c r="P90">
-        <v>-5.547371200000001</v>
+        <v>-5.618818599999999</v>
       </c>
       <c r="Q90">
-        <v>-3.567371200000001</v>
+        <v>-3.638818599999999</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4084436897814815</v>
+        <v>0.4414112979434344</v>
       </c>
       <c r="T90">
-        <v>5.609982546405648</v>
+        <v>6.119980959715253</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.02942406199907523</v>
+        <v>0.02909345456088338</v>
       </c>
       <c r="W90">
-        <v>0.2288618061806181</v>
+        <v>0.2289397634145437</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.1176962479963009</v>
+        <v>0.1163738182435334</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2523116322127217</v>
+        <v>0.2542116322127217</v>
       </c>
       <c r="C91">
-        <v>-27.78287048289323</v>
+        <v>-28.25960368843251</v>
       </c>
       <c r="D91">
-        <v>7.978129517106767</v>
+        <v>7.905396311567494</v>
       </c>
       <c r="E91">
-        <v>12.056</v>
+        <v>12.46</v>
       </c>
       <c r="F91">
-        <v>35.956</v>
+        <v>36.36</v>
       </c>
       <c r="G91">
         <v>0.195</v>
@@ -8743,37 +8743,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M91">
-        <v>8.478424799999999</v>
+        <v>8.573688000000001</v>
       </c>
       <c r="N91">
-        <v>-7.491758133333333</v>
+        <v>-7.587021333333334</v>
       </c>
       <c r="O91">
-        <v>-1.872939533333333</v>
+        <v>-1.896755333333334</v>
       </c>
       <c r="P91">
-        <v>-5.618818599999999</v>
+        <v>-5.690266000000001</v>
       </c>
       <c r="Q91">
-        <v>-3.638818599999999</v>
+        <v>-3.710266000000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4414112979434344</v>
+        <v>0.4809724277377779</v>
       </c>
       <c r="T91">
-        <v>6.119980959715253</v>
+        <v>6.731979055686779</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.02909345456088338</v>
+        <v>0.02877019395465133</v>
       </c>
       <c r="W91">
-        <v>0.2289397634145437</v>
+        <v>0.2290159882654932</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.1163738182435334</v>
+        <v>0.1150807758186053</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2542116322127217</v>
+        <v>0.2561116322127217</v>
       </c>
       <c r="C92">
-        <v>-28.25960368843251</v>
+        <v>-28.73502271948632</v>
       </c>
       <c r="D92">
-        <v>7.905396311567494</v>
+        <v>7.833977280513682</v>
       </c>
       <c r="E92">
-        <v>12.46</v>
+        <v>12.864</v>
       </c>
       <c r="F92">
-        <v>36.36</v>
+        <v>36.764</v>
       </c>
       <c r="G92">
         <v>0.195</v>
@@ -8825,37 +8825,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M92">
-        <v>8.573688000000001</v>
+        <v>8.6689512</v>
       </c>
       <c r="N92">
-        <v>-7.587021333333334</v>
+        <v>-7.682284533333334</v>
       </c>
       <c r="O92">
-        <v>-1.896755333333334</v>
+        <v>-1.920571133333334</v>
       </c>
       <c r="P92">
-        <v>-5.690266000000001</v>
+        <v>-5.761713400000001</v>
       </c>
       <c r="Q92">
-        <v>-3.710266000000001</v>
+        <v>-3.781713400000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.4809724277377779</v>
+        <v>0.5293249197086421</v>
       </c>
       <c r="T92">
-        <v>6.731979055686779</v>
+        <v>7.479976728540866</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.02877019395465133</v>
+        <v>0.02845403797712769</v>
       </c>
       <c r="W92">
-        <v>0.2290159882654932</v>
+        <v>0.2290905378449933</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.1150807758186053</v>
+        <v>0.1138161519085107</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2561116322127217</v>
+        <v>0.2580116322127217</v>
       </c>
       <c r="C93">
-        <v>-28.73502271948632</v>
+        <v>-29.20916287475384</v>
       </c>
       <c r="D93">
-        <v>7.833977280513682</v>
+        <v>7.763837125246155</v>
       </c>
       <c r="E93">
-        <v>12.864</v>
+        <v>13.268</v>
       </c>
       <c r="F93">
-        <v>36.764</v>
+        <v>37.168</v>
       </c>
       <c r="G93">
         <v>0.195</v>
@@ -8907,37 +8907,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M93">
-        <v>8.6689512</v>
+        <v>8.7642144</v>
       </c>
       <c r="N93">
-        <v>-7.682284533333334</v>
+        <v>-7.777547733333334</v>
       </c>
       <c r="O93">
-        <v>-1.920571133333334</v>
+        <v>-1.944386933333333</v>
       </c>
       <c r="P93">
-        <v>-5.761713400000001</v>
+        <v>-5.8331608</v>
       </c>
       <c r="Q93">
-        <v>-3.781713400000001</v>
+        <v>-3.8531608</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5293249197086421</v>
+        <v>0.5897655346722225</v>
       </c>
       <c r="T93">
-        <v>7.479976728540866</v>
+        <v>8.414973819608477</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.02845403797712769</v>
+        <v>0.02814475495563717</v>
       </c>
       <c r="W93">
-        <v>0.2290905378449933</v>
+        <v>0.2291634667814608</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.1138161519085107</v>
+        <v>0.1125790198225487</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2580116322127217</v>
+        <v>0.2599116322127217</v>
       </c>
       <c r="C94">
-        <v>-29.20916287475384</v>
+        <v>-29.6820581999892</v>
       </c>
       <c r="D94">
-        <v>7.763837125246155</v>
+        <v>7.694941800010803</v>
       </c>
       <c r="E94">
-        <v>13.268</v>
+        <v>13.672</v>
       </c>
       <c r="F94">
-        <v>37.168</v>
+        <v>37.572</v>
       </c>
       <c r="G94">
         <v>0.195</v>
@@ -8989,37 +8989,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M94">
-        <v>8.7642144</v>
+        <v>8.859477600000002</v>
       </c>
       <c r="N94">
-        <v>-7.777547733333334</v>
+        <v>-7.872810933333335</v>
       </c>
       <c r="O94">
-        <v>-1.944386933333333</v>
+        <v>-1.968202733333334</v>
       </c>
       <c r="P94">
-        <v>-5.8331608</v>
+        <v>-5.904608200000002</v>
       </c>
       <c r="Q94">
-        <v>-3.8531608</v>
+        <v>-3.924608200000002</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.5897655346722225</v>
+        <v>0.6674748967682544</v>
       </c>
       <c r="T94">
-        <v>8.414973819608477</v>
+        <v>9.617112936695404</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.02814475495563717</v>
+        <v>0.02784212318192064</v>
       </c>
       <c r="W94">
-        <v>0.2291634667814608</v>
+        <v>0.2292348273537031</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1125790198225487</v>
+        <v>0.1113684927276826</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2599116322127217</v>
+        <v>0.2618116322127217</v>
       </c>
       <c r="C95">
-        <v>-29.6820581999892</v>
+        <v>-30.15374154310482</v>
       </c>
       <c r="D95">
-        <v>7.694941800010803</v>
+        <v>7.627258456895175</v>
       </c>
       <c r="E95">
-        <v>13.672</v>
+        <v>14.076</v>
       </c>
       <c r="F95">
-        <v>37.572</v>
+        <v>37.976</v>
       </c>
       <c r="G95">
         <v>0.195</v>
@@ -9071,37 +9071,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M95">
-        <v>8.859477600000002</v>
+        <v>8.9547408</v>
       </c>
       <c r="N95">
-        <v>-7.872810933333335</v>
+        <v>-7.968074133333333</v>
       </c>
       <c r="O95">
-        <v>-1.968202733333334</v>
+        <v>-1.992018533333333</v>
       </c>
       <c r="P95">
-        <v>-5.904608200000002</v>
+        <v>-5.9760556</v>
       </c>
       <c r="Q95">
-        <v>-3.924608200000002</v>
+        <v>-3.9960556</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6674748967682544</v>
+        <v>0.7710873795629637</v>
       </c>
       <c r="T95">
-        <v>9.617112936695404</v>
+        <v>11.21996509281131</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.02784212318192064</v>
+        <v>0.02754593038211298</v>
       </c>
       <c r="W95">
-        <v>0.2292348273537031</v>
+        <v>0.2293046696158978</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1113684927276826</v>
+        <v>0.1101837215284519</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2618116322127217</v>
+        <v>0.2637116322127217</v>
       </c>
       <c r="C96">
-        <v>-30.15374154310482</v>
+        <v>-30.62424460639222</v>
       </c>
       <c r="D96">
-        <v>7.627258456895175</v>
+        <v>7.560755393607784</v>
       </c>
       <c r="E96">
-        <v>14.076</v>
+        <v>14.48</v>
       </c>
       <c r="F96">
-        <v>37.976</v>
+        <v>38.38</v>
       </c>
       <c r="G96">
         <v>0.195</v>
@@ -9153,37 +9153,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M96">
-        <v>8.9547408</v>
+        <v>9.050004000000001</v>
       </c>
       <c r="N96">
-        <v>-7.968074133333333</v>
+        <v>-8.063337333333335</v>
       </c>
       <c r="O96">
-        <v>-1.992018533333333</v>
+        <v>-2.015834333333334</v>
       </c>
       <c r="P96">
-        <v>-5.9760556</v>
+        <v>-6.047503000000001</v>
       </c>
       <c r="Q96">
-        <v>-3.9960556</v>
+        <v>-4.067503</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.7710873795629637</v>
+        <v>0.9161448554755568</v>
       </c>
       <c r="T96">
-        <v>11.21996509281131</v>
+        <v>13.46395811137358</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.02754593038211298</v>
+        <v>0.027255973220196</v>
       </c>
       <c r="W96">
-        <v>0.2293046696158978</v>
+        <v>0.2293730415146778</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.1101837215284519</v>
+        <v>0.109023892880784</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2637116322127217</v>
+        <v>0.2656116322127217</v>
       </c>
       <c r="C97">
-        <v>-30.62424460639222</v>
+        <v>-31.09359799603427</v>
       </c>
       <c r="D97">
-        <v>7.560755393607784</v>
+        <v>7.495402003965729</v>
       </c>
       <c r="E97">
-        <v>14.48</v>
+        <v>14.884</v>
       </c>
       <c r="F97">
-        <v>38.38</v>
+        <v>38.784</v>
       </c>
       <c r="G97">
         <v>0.195</v>
@@ -9235,37 +9235,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M97">
-        <v>9.050004000000001</v>
+        <v>9.145267199999999</v>
       </c>
       <c r="N97">
-        <v>-8.063337333333335</v>
+        <v>-8.158600533333333</v>
       </c>
       <c r="O97">
-        <v>-2.015834333333334</v>
+        <v>-2.039650133333333</v>
       </c>
       <c r="P97">
-        <v>-6.047503000000001</v>
+        <v>-6.118950399999999</v>
       </c>
       <c r="Q97">
-        <v>-4.067503</v>
+        <v>-4.138950399999999</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9161448554755568</v>
+        <v>1.133731069344446</v>
       </c>
       <c r="T97">
-        <v>13.46395811137358</v>
+        <v>16.82994763921698</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.027255973220196</v>
+        <v>0.02697205683248563</v>
       </c>
       <c r="W97">
-        <v>0.2293730415146778</v>
+        <v>0.2294399889988999</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.109023892880784</v>
+        <v>0.1078882273299425</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2656116322127217</v>
+        <v>0.2675116322127217</v>
       </c>
       <c r="C98">
-        <v>-31.09359799603427</v>
+        <v>-31.56183126907188</v>
       </c>
       <c r="D98">
-        <v>7.495402003965729</v>
+        <v>7.431168730928111</v>
       </c>
       <c r="E98">
-        <v>14.884</v>
+        <v>15.288</v>
       </c>
       <c r="F98">
-        <v>38.784</v>
+        <v>39.188</v>
       </c>
       <c r="G98">
         <v>0.195</v>
@@ -9317,37 +9317,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M98">
-        <v>9.145267199999999</v>
+        <v>9.240530399999999</v>
       </c>
       <c r="N98">
-        <v>-8.158600533333333</v>
+        <v>-8.253863733333333</v>
       </c>
       <c r="O98">
-        <v>-2.039650133333333</v>
+        <v>-2.063465933333333</v>
       </c>
       <c r="P98">
-        <v>-6.118950399999999</v>
+        <v>-6.1903978</v>
       </c>
       <c r="Q98">
-        <v>-4.138950399999999</v>
+        <v>-4.210397799999999</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.133731069344444</v>
+        <v>1.496374759125925</v>
       </c>
       <c r="T98">
-        <v>16.82994763921693</v>
+        <v>22.43993018562258</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.02697205683248563</v>
+        <v>0.02669399439091361</v>
       </c>
       <c r="W98">
-        <v>0.2294399889988999</v>
+        <v>0.2295055561226226</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1078882273299425</v>
+        <v>0.1067759775636544</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2675116322127217</v>
+        <v>0.2694116322127217</v>
       </c>
       <c r="C99">
-        <v>-31.56183126907188</v>
+        <v>-32.02897297797606</v>
       </c>
       <c r="D99">
-        <v>7.431168730928111</v>
+        <v>7.368027022023936</v>
       </c>
       <c r="E99">
-        <v>15.288</v>
+        <v>15.692</v>
       </c>
       <c r="F99">
-        <v>39.188</v>
+        <v>39.592</v>
       </c>
       <c r="G99">
         <v>0.195</v>
@@ -9399,37 +9399,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M99">
-        <v>9.240530399999999</v>
+        <v>9.335793600000001</v>
       </c>
       <c r="N99">
-        <v>-8.253863733333333</v>
+        <v>-8.349126933333334</v>
       </c>
       <c r="O99">
-        <v>-2.063465933333333</v>
+        <v>-2.087281733333334</v>
       </c>
       <c r="P99">
-        <v>-6.1903978</v>
+        <v>-6.261845200000001</v>
       </c>
       <c r="Q99">
-        <v>-4.210397799999999</v>
+        <v>-4.281845200000001</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.496374759125925</v>
+        <v>2.221662138688887</v>
       </c>
       <c r="T99">
-        <v>22.43993018562258</v>
+        <v>33.65989527843386</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.02669399439091361</v>
+        <v>0.02642160669304714</v>
       </c>
       <c r="W99">
-        <v>0.2295055561226226</v>
+        <v>0.2295697851417795</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1067759775636544</v>
+        <v>0.1056864267721885</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2694116322127217</v>
+        <v>0.2713116322127217</v>
       </c>
       <c r="C100">
-        <v>-32.02897297797606</v>
+        <v>-32.49505071296687</v>
       </c>
       <c r="D100">
-        <v>7.368027022023936</v>
+        <v>7.305949287033129</v>
       </c>
       <c r="E100">
-        <v>15.692</v>
+        <v>16.096</v>
       </c>
       <c r="F100">
-        <v>39.592</v>
+        <v>39.996</v>
       </c>
       <c r="G100">
         <v>0.195</v>
@@ -9481,37 +9481,37 @@
         <v>0.9866666666666668</v>
       </c>
       <c r="M100">
-        <v>9.335793600000001</v>
+        <v>9.431056799999999</v>
       </c>
       <c r="N100">
-        <v>-8.349126933333334</v>
+        <v>-8.444390133333332</v>
       </c>
       <c r="O100">
-        <v>-2.087281733333334</v>
+        <v>-2.111097533333333</v>
       </c>
       <c r="P100">
-        <v>-6.261845200000001</v>
+        <v>-6.333292599999999</v>
       </c>
       <c r="Q100">
-        <v>-4.281845200000001</v>
+        <v>-4.3532926</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.221662138688887</v>
+        <v>4.397524277377774</v>
       </c>
       <c r="T100">
-        <v>33.65989527843386</v>
+        <v>67.31979055686772</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.02642160669304714</v>
+        <v>0.02615472177695576</v>
       </c>
       <c r="W100">
-        <v>0.2295697851417795</v>
+        <v>0.2296327166049938</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1056864267721885</v>
+        <v>0.104618887107823</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2713116322127217</v>
-      </c>
-      <c r="C101">
-        <v>-32.49505071296687</v>
-      </c>
-      <c r="D101">
-        <v>7.305949287033129</v>
-      </c>
-      <c r="E101">
-        <v>16.096</v>
-      </c>
-      <c r="F101">
-        <v>39.996</v>
-      </c>
-      <c r="G101">
-        <v>0.195</v>
-      </c>
-      <c r="H101">
-        <v>16.5</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>2.966666666666667</v>
-      </c>
-      <c r="K101">
-        <v>1.98</v>
-      </c>
-      <c r="L101">
-        <v>0.9866666666666668</v>
-      </c>
-      <c r="M101">
-        <v>9.431056799999999</v>
-      </c>
-      <c r="N101">
-        <v>-8.444390133333332</v>
-      </c>
-      <c r="O101">
-        <v>-2.111097533333333</v>
-      </c>
-      <c r="P101">
-        <v>-6.333292599999999</v>
-      </c>
-      <c r="Q101">
-        <v>-4.3532926</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.397524277377774</v>
-      </c>
-      <c r="T101">
-        <v>67.31979055686772</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.02615472177695576</v>
-      </c>
-      <c r="W101">
-        <v>0.2296327166049938</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.104618887107823</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
